--- a/submission/2025-2026-HK3-Group52-Project_Evaluation.xlsx
+++ b/submission/2025-2026-HK3-Group52-Project_Evaluation.xlsx
@@ -1,159 +1,459 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Summary" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Tasks" sheetId="2" r:id="rId6"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Tasks" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
-  <si>
-    <t>Course</t>
-  </si>
-  <si>
-    <t>A task should be done by only 1-2 students. Duplicate tasks are not recommended
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="115">
+  <si>
+    <t xml:space="preserve">Course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS202 - C++ Programming / Design Patterns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25A01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROJECT CONTRIBUTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of students working in the project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of tasks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of task hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Git commits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max student percentage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do not edit the grey cells. TAs will enter the score of all PAs in the project score and get the individual scores. Students can enter an estimated project score to see how percentages affects your scores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use columns Tasks - Percent, Task Hours - Percent, Git - Percent as references for column Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tasks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tasks - Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task Hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task Hours - Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git Commits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git - Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score - Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score - TA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25125083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Đình Minh Huy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25125084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trần Gia Huy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A task should be done by only 1-2 students. Duplicate tasks are not recommended
 Each member should work on at least 5 tasks</t>
   </si>
   <si>
-    <t>Class</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>PROJECT CONTRIBUTION</t>
-  </si>
-  <si>
-    <t>Student ID</t>
-  </si>
-  <si>
-    <t>Full name</t>
-  </si>
-  <si>
-    <t>Task Description</t>
-  </si>
-  <si>
-    <t>Hours</t>
-  </si>
-  <si>
-    <t>Evidence (screenshots of chat messages, of Git commits... proving that you perform and finish the task)</t>
-  </si>
-  <si>
-    <t>Number of students working in the project</t>
-  </si>
-  <si>
-    <t>Number of tasks</t>
-  </si>
-  <si>
-    <t>Number of task hours</t>
-  </si>
-  <si>
-    <t>Number of Git commits</t>
-  </si>
-  <si>
-    <t>Max student percentage</t>
-  </si>
-  <si>
-    <t>Project score</t>
-  </si>
-  <si>
-    <t>Do not edit the grey cells. TAs will enter the score of all PAs in the project score and get the individual scores. Students can enter an estimated project score to see how percentages affects your scores</t>
-  </si>
-  <si>
-    <t>Use columns Tasks - Percent, Task Hours - Percent, Git - Percent as references for column Percent</t>
-  </si>
-  <si>
-    <t>Tasks</t>
-  </si>
-  <si>
-    <t>Tasks - Percent</t>
-  </si>
-  <si>
-    <t>Task Hours</t>
-  </si>
-  <si>
-    <t>Task Hours - Percent</t>
-  </si>
-  <si>
-    <t>Git Commits</t>
-  </si>
-  <si>
-    <t>Git - Percent</t>
-  </si>
-  <si>
-    <t>Percent</t>
-  </si>
-  <si>
-    <t>Score - Student</t>
-  </si>
-  <si>
-    <t>Score - TA</t>
+    <t xml:space="preserve">Task Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence (screenshots of chat messages, of Git commits... proving that you perform and finish the task)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scaffold project structure with empty C++ source files for all three patterns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit b16678d - Empty C++ files across the workspace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draft task division plan, presentation script, and PDF documentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit a442d9c - Add task division plan, presentation script, and PDF documentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transition Observer example to Bank Account scenario; add AGENTS.md contribution guidelines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commits 5fcf47f, 040e906, 876ef03 - docs(observer): update example to Bank Account notifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implement Observer pattern.cpp (AccountObserver/BankAccount) and dual-pathway main.cpp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit 13dacd7 - feat(observer): implement pattern.cpp and dual-pathway main.cpp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Make Observer pattern demo interactive with step-by-step prompts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit 4da8605 - feat(observer): make pattern demo interactive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implement automatic agent prompt-logging system described in AGENTS.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit 1231981 - docs: implement automatic prompt logging system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add withdrawal and failed-transaction scenarios to Observer demo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit 1dd0e2f - feat(observer): add withdrawal and failed transaction scenarios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design and integrate general + specific Observer UML class diagrams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit 8959cc2 - Design and integrate general and specific UML class diagrams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redesign Observer UML/console figures for clarity (compact layout, sequence diagram, GoF structure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commits aebbbd5, 8a922c3, 67054c2, 6147a60, d7161d3 - agent_history.log 2026-07-20 08:49-08:58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build TikZ/Graphviz process flowcharts for the Observer notification flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commits ccd2881, f9712dc, 03eb14e, 20681de - agent_history.log 2026-07-20 09:01-09:13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Convert and optimize Observer-Mediator Fusion UML (TikZ to Graphviz, layout)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commits b736161, da8e6b2, eabe230 - agent_history.log 2026-07-20 09:59-10:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Convert Bank Account flowchart to Graphviz DOT format</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit 4e1e134 - Convert Bank Account flowchart from TikZ to Graphviz DOT format</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add Super Mario Game EventBus case study to Observer report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit c57070a - Add Super Mario Game EventBus case study</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regenerate terminal console screenshots in light theme and embed in report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commits 82fe305, 8e243bf - agent_history.log 2026-07-20 10:17-10:20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add pattern/naive/concrete-observer code header screenshots to Observer report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commits 6bfc1d2, b2b56b9 - agent_history.log 2026-07-23 00:58-01:01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Move Observer presentation into repo and build a modern-design rebuild deck (47 slides)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit 2eb3cfd - docs(observer): add original presentation and a modern-design rebuild</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expand Observer report quiz and add Observer-Interpreter fusion section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit 4001bc6 - docs(observer): expand report quiz, add Interpreter fusion section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sync AgentHub rules and add CLAUDE.md pointer to AGENTS.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit 6b85320 - docs(agents): sync AgentHub universal rules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Update AGENTS.md rules/gitignore and merge latest origin/main updates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commits a1784f6, bb551c8 - agent_history.log 2026-08-27 13:52-13:55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implement Mediator naive.cpp (O(N^2) mesh) and pattern.cpp (ATCTower mediator) with main.cpp driver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit 6a65b75 - feat(mediator): implement C++17 ATC simulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Author complete 23-page Mediator LaTeX report and sync quizzes across all reports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit ef1ca44 - docs(reports): author complete Mediator report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align report structure with reference by removing quiz sections from LaTeX reports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit cf8cb2a - docs(reports): align report structure with reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix LaTeX overlapping diagrams and overfull hboxes in Mediator report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit fbb6c20 - fix: resolve LaTeX overlapping diagrams and overfull hboxes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write AI Usage Declaration and Changes.md; rename evaluation template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit 4b74200 - docs: add AI Usage Declaration, Changes.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rework UML diagram spacing and assemble final submission folder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit 9c71936 - fix: rework UML diagrams, assemble submission folder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix missing arrowheads and overlapping inheritance arrows in Figure 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commits 552f860, 0d3766a - fix: add/resolve arrowheads and overlapping arrows in Figure 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resolve Mediator UML compile error and cross-report layout defects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit cf05a9b - fix: resolve Mediator UML compile error and cross-report layout defects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Update README with new group member information</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit b3a78c1 - Update README with new group member information</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implement naive Observer solution (NaiveBankAccount) and analyze its tight coupling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit bcd8950 - feat: implement naive solution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design Class UML for the Observer naive solution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commits 1eaff6b, 2e14891 - Create Class UML for naive solution / Update UML file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draft Observer presentation slides sections 1-4 (Problem, Naive code, Drawbacks, Pattern Intro)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit 0899017 - Update naive UML. Create slide from section 1 to 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Include Interpreter pattern usage example in presentation slides</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit d788b33 - Include usage with interpreter in slide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Update Observer report to the new Bank Account example problem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit cf9aeaf - Update the report to the new example problem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Update .gitignore to exclude build artifacts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit ba0116c - Update gitignore to exclude artifact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build Observer presentation deck (ObserverG52.pptx)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit a7eccce - feat: observer presentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implement full Interpreter pattern C++ source (naive.cpp, pattern.cpp, main.cpp)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit d36c823 - feat: implement the test source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Author LaTeX reports for the Interpreter and Observer patterns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit 88ea176 - feat: report for interpreter and observer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revise reports (version 2): trim wording, fix UML diagrams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit 4d46af6 - feat: report version 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix remaining UML diagram and title issues in Interpreter/Observer reports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commit c83aebc - fix: fix some uml and titles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resolve merge conflicts while pulling latest changes and merge into main</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git commits 72b13c6, a522007, 75e9cbb - merge conflict resolution with main</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0%"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="11">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <i/>
+      <b val="true"/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <i val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16.0"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -161,105 +461,204 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor theme="4"/>
+        <bgColor rgb="FF666699"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFEFEFEF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEFEFEF"/>
-        <bgColor rgb="FFEFEFEF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="18">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="9" xfId="0" applyFill="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="6" numFmtId="9" xfId="0" applyFill="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="164" xfId="0" applyFill="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="4" fontId="6" numFmtId="9" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFEFEFEF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFD9D9D9"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF4285F4"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -305,59 +704,55 @@
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -365,33 +760,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -404,13 +790,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -420,15 +800,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -436,7 +814,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -444,11 +821,11 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -457,4294 +834,4277 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:L1010"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="37.63"/>
-    <col customWidth="1" min="5" max="9" width="18.88"/>
-    <col customWidth="1" min="11" max="11" width="18.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="37.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="5" style="1" width="18.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="18.88"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B1" s="2" t="s">
         <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
     </row>
-    <row r="2">
-      <c r="B2" s="1" t="s">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
         <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
     </row>
-    <row r="3">
-      <c r="B3" s="1" t="s">
-        <v>3</v>
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
     </row>
-    <row r="4" ht="39.0" customHeight="1">
-      <c r="A4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
+    <row r="4" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
     </row>
-    <row r="5">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
     </row>
-    <row r="6">
-      <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="9">
-        <v>5.0</v>
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>2</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
     </row>
-    <row r="7">
-      <c r="C7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="10">
-        <f>SUM(D17:D25)</f>
-        <v>50</v>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <f aca="false">SUM(D17:D25)</f>
+        <v>40</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8">
-      <c r="C8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="10">
-        <f>SUM(F17:F25)</f>
-        <v>300</v>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <f aca="false">SUM(F17:F25)</f>
+        <v>78</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
     </row>
-    <row r="9">
-      <c r="C9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="10">
-        <f>SUM(H17:H25)</f>
-        <v>100</v>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <f aca="false">SUM(H17:H25)</f>
+        <v>79</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
     </row>
-    <row r="10">
-      <c r="C10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="11">
-        <f>MAX((J17:J25))</f>
-        <v>0.25</v>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <f aca="false">MAX((J17:J25))</f>
+        <v>0.5</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
     </row>
-    <row r="11">
-      <c r="C11" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="13">
-        <v>10.0</v>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
     </row>
-    <row r="12">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
     </row>
-    <row r="13">
-      <c r="A13" s="14" t="s">
-        <v>17</v>
-      </c>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
       <c r="K13" s="3"/>
     </row>
-    <row r="14">
-      <c r="A14" s="15" t="s">
-        <v>18</v>
-      </c>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
       <c r="K14" s="3"/>
     </row>
-    <row r="15">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="4" t="s">
+    <row r="16" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="F16" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="G16" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="H16" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="I16" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="J16" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="K16" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="K16" s="4" t="s">
+      <c r="L16" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="L16" s="4" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="16">
-        <v>1.0</v>
-      </c>
-      <c r="D17" s="16">
-        <v>10.0</v>
-      </c>
-      <c r="E17" s="11">
-        <f t="shared" ref="E17:E21" si="1">IF($D$7=0, 0, D17/$D$7)</f>
-        <v>0.2</v>
-      </c>
-      <c r="F17" s="16">
-        <v>60.0</v>
-      </c>
-      <c r="G17" s="11">
-        <f t="shared" ref="G17:G21" si="2">IF($D$8=0, 0, F17/$D$8)</f>
-        <v>0.2</v>
-      </c>
-      <c r="H17" s="16">
-        <v>20.0</v>
-      </c>
-      <c r="I17" s="17">
-        <f t="shared" ref="I17:I19" si="3">if($D$9 = 0, 0, H17/$D$9)</f>
-        <v>0.2</v>
-      </c>
-      <c r="J17" s="18">
-        <v>0.15</v>
-      </c>
-      <c r="K17" s="19">
-        <f t="shared" ref="K17:K21" si="4">if(J17=$D$10, $D$11, ROUND(2 * ($D$11 - 1 * $D$11 * (1-J17/$D$10)),0)/2)</f>
-        <v>6</v>
-      </c>
-      <c r="L17" s="10"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="16">
-        <v>2.0</v>
-      </c>
-      <c r="D18" s="16">
-        <v>10.0</v>
-      </c>
-      <c r="E18" s="11">
-        <f t="shared" si="1"/>
-        <v>0.2</v>
-      </c>
-      <c r="F18" s="16">
-        <v>60.0</v>
-      </c>
-      <c r="G18" s="11">
-        <f t="shared" si="2"/>
-        <v>0.2</v>
-      </c>
-      <c r="H18" s="16">
-        <v>20.0</v>
-      </c>
-      <c r="I18" s="17">
-        <f t="shared" si="3"/>
-        <v>0.2</v>
-      </c>
-      <c r="J18" s="18">
-        <v>0.15</v>
-      </c>
-      <c r="K18" s="19">
-        <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="L18" s="10"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="16">
-        <v>3.0</v>
-      </c>
-      <c r="D19" s="16">
-        <v>10.0</v>
-      </c>
-      <c r="E19" s="11">
-        <f t="shared" si="1"/>
-        <v>0.2</v>
-      </c>
-      <c r="F19" s="16">
-        <v>60.0</v>
-      </c>
-      <c r="G19" s="11">
-        <f t="shared" si="2"/>
-        <v>0.2</v>
-      </c>
-      <c r="H19" s="16">
-        <v>20.0</v>
-      </c>
-      <c r="I19" s="17">
-        <f t="shared" si="3"/>
-        <v>0.2</v>
-      </c>
-      <c r="J19" s="18">
-        <v>0.2</v>
-      </c>
-      <c r="K19" s="19">
-        <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="L19" s="10"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="16">
-        <v>4.0</v>
-      </c>
-      <c r="D20" s="16">
-        <v>10.0</v>
-      </c>
-      <c r="E20" s="11">
-        <f t="shared" si="1"/>
-        <v>0.2</v>
-      </c>
-      <c r="F20" s="16">
-        <v>60.0</v>
-      </c>
-      <c r="G20" s="11">
-        <f t="shared" si="2"/>
-        <v>0.2</v>
-      </c>
-      <c r="H20" s="16">
-        <v>20.0</v>
-      </c>
-      <c r="I20" s="20">
-        <v>0.25</v>
-      </c>
-      <c r="J20" s="18">
-        <v>0.25</v>
-      </c>
-      <c r="K20" s="19">
-        <f t="shared" si="4"/>
+      <c r="C17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <f aca="false">IF($D$7=0, 0, D17/$D$7)</f>
+        <v>0.675</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <f aca="false">IF($D$8=0, 0, F17/$D$8)</f>
+        <v>0.666666666666667</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="I17" s="13" t="n">
+        <f aca="false">IF($D$9 = 0, 0, H17/$D$9)</f>
+        <v>0.683544303797468</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K17" s="15" t="n">
+        <f aca="false">IF(J17=$D$10, $D$11, ROUND(2 * ($D$11 - 1 * $D$11 * (1-J17/$D$10)),0)/2)</f>
         <v>10</v>
       </c>
-      <c r="L20" s="10"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="16">
-        <v>5.0</v>
-      </c>
-      <c r="D21" s="16">
-        <v>10.0</v>
-      </c>
-      <c r="E21" s="11">
-        <f t="shared" si="1"/>
-        <v>0.2</v>
-      </c>
-      <c r="F21" s="16">
-        <v>60.0</v>
-      </c>
-      <c r="G21" s="11">
-        <f t="shared" si="2"/>
-        <v>0.2</v>
-      </c>
-      <c r="H21" s="16">
-        <v>20.0</v>
-      </c>
-      <c r="I21" s="20">
-        <v>0.25</v>
-      </c>
-      <c r="J21" s="18">
-        <v>0.25</v>
-      </c>
-      <c r="K21" s="19">
-        <f t="shared" si="4"/>
+      <c r="L17" s="6"/>
+    </row>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <f aca="false">IF($D$7=0, 0, D18/$D$7)</f>
+        <v>0.325</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <f aca="false">IF($D$8=0, 0, F18/$D$8)</f>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="I18" s="13" t="n">
+        <f aca="false">IF($D$9 = 0, 0, H18/$D$9)</f>
+        <v>0.316455696202532</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K18" s="15" t="n">
+        <f aca="false">IF(J18=$D$10, $D$11, ROUND(2 * ($D$11 - 1 * $D$11 * (1-J18/$D$10)),0)/2)</f>
         <v>10</v>
       </c>
-      <c r="L21" s="10"/>
-    </row>
-    <row r="22">
+      <c r="L18" s="6"/>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="6"/>
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="6"/>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="6"/>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
     </row>
-    <row r="23">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
     </row>
-    <row r="24">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
     </row>
-    <row r="25">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
     </row>
-    <row r="26">
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
     </row>
-    <row r="27">
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
     </row>
-    <row r="28">
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
     </row>
-    <row r="29">
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
     </row>
-    <row r="30">
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
     </row>
-    <row r="31">
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
     </row>
-    <row r="32">
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
     </row>
-    <row r="33">
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
     </row>
-    <row r="34">
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
     </row>
-    <row r="35">
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
     </row>
-    <row r="36">
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J36" s="3"/>
       <c r="K36" s="3"/>
     </row>
-    <row r="37">
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
     </row>
-    <row r="38">
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
     </row>
-    <row r="39">
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
     </row>
-    <row r="40">
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
     </row>
-    <row r="41">
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
     </row>
-    <row r="42">
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
     </row>
-    <row r="43">
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J43" s="3"/>
       <c r="K43" s="3"/>
     </row>
-    <row r="44">
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
     </row>
-    <row r="45">
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
     </row>
-    <row r="46">
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J46" s="3"/>
       <c r="K46" s="3"/>
     </row>
-    <row r="47">
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J47" s="3"/>
       <c r="K47" s="3"/>
     </row>
-    <row r="48">
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
     </row>
-    <row r="49">
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
     </row>
-    <row r="50">
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
     </row>
-    <row r="51">
+    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
     </row>
-    <row r="52">
+    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J52" s="3"/>
       <c r="K52" s="3"/>
     </row>
-    <row r="53">
+    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
     </row>
-    <row r="54">
+    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
     </row>
-    <row r="55">
+    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
     </row>
-    <row r="56">
+    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
     </row>
-    <row r="57">
+    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J57" s="3"/>
       <c r="K57" s="3"/>
     </row>
-    <row r="58">
+    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J58" s="3"/>
       <c r="K58" s="3"/>
     </row>
-    <row r="59">
+    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J59" s="3"/>
       <c r="K59" s="3"/>
     </row>
-    <row r="60">
+    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J60" s="3"/>
       <c r="K60" s="3"/>
     </row>
-    <row r="61">
+    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J61" s="3"/>
       <c r="K61" s="3"/>
     </row>
-    <row r="62">
+    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
     </row>
-    <row r="63">
+    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J63" s="3"/>
       <c r="K63" s="3"/>
     </row>
-    <row r="64">
+    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J64" s="3"/>
       <c r="K64" s="3"/>
     </row>
-    <row r="65">
+    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J65" s="3"/>
       <c r="K65" s="3"/>
     </row>
-    <row r="66">
+    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J66" s="3"/>
       <c r="K66" s="3"/>
     </row>
-    <row r="67">
+    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
     </row>
-    <row r="68">
+    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J68" s="3"/>
       <c r="K68" s="3"/>
     </row>
-    <row r="69">
+    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J69" s="3"/>
       <c r="K69" s="3"/>
     </row>
-    <row r="70">
+    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J70" s="3"/>
       <c r="K70" s="3"/>
     </row>
-    <row r="71">
+    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J71" s="3"/>
       <c r="K71" s="3"/>
     </row>
-    <row r="72">
+    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J72" s="3"/>
       <c r="K72" s="3"/>
     </row>
-    <row r="73">
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J73" s="3"/>
       <c r="K73" s="3"/>
     </row>
-    <row r="74">
+    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J74" s="3"/>
       <c r="K74" s="3"/>
     </row>
-    <row r="75">
+    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J75" s="3"/>
       <c r="K75" s="3"/>
     </row>
-    <row r="76">
+    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J76" s="3"/>
       <c r="K76" s="3"/>
     </row>
-    <row r="77">
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J77" s="3"/>
       <c r="K77" s="3"/>
     </row>
-    <row r="78">
+    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J78" s="3"/>
       <c r="K78" s="3"/>
     </row>
-    <row r="79">
+    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J79" s="3"/>
       <c r="K79" s="3"/>
     </row>
-    <row r="80">
+    <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J80" s="3"/>
       <c r="K80" s="3"/>
     </row>
-    <row r="81">
+    <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J81" s="3"/>
       <c r="K81" s="3"/>
     </row>
-    <row r="82">
+    <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
     </row>
-    <row r="83">
+    <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J83" s="3"/>
       <c r="K83" s="3"/>
     </row>
-    <row r="84">
+    <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J84" s="3"/>
       <c r="K84" s="3"/>
     </row>
-    <row r="85">
+    <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J85" s="3"/>
       <c r="K85" s="3"/>
     </row>
-    <row r="86">
+    <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J86" s="3"/>
       <c r="K86" s="3"/>
     </row>
-    <row r="87">
+    <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J87" s="3"/>
       <c r="K87" s="3"/>
     </row>
-    <row r="88">
+    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J88" s="3"/>
       <c r="K88" s="3"/>
     </row>
-    <row r="89">
+    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J89" s="3"/>
       <c r="K89" s="3"/>
     </row>
-    <row r="90">
+    <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
     </row>
-    <row r="91">
+    <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J91" s="3"/>
       <c r="K91" s="3"/>
     </row>
-    <row r="92">
+    <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J92" s="3"/>
       <c r="K92" s="3"/>
     </row>
-    <row r="93">
+    <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J93" s="3"/>
       <c r="K93" s="3"/>
     </row>
-    <row r="94">
+    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J94" s="3"/>
       <c r="K94" s="3"/>
     </row>
-    <row r="95">
+    <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
     </row>
-    <row r="96">
+    <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J96" s="3"/>
       <c r="K96" s="3"/>
     </row>
-    <row r="97">
+    <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J97" s="3"/>
       <c r="K97" s="3"/>
     </row>
-    <row r="98">
+    <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J98" s="3"/>
       <c r="K98" s="3"/>
     </row>
-    <row r="99">
+    <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J99" s="3"/>
       <c r="K99" s="3"/>
     </row>
-    <row r="100">
+    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J100" s="3"/>
       <c r="K100" s="3"/>
     </row>
-    <row r="101">
+    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J101" s="3"/>
       <c r="K101" s="3"/>
     </row>
-    <row r="102">
+    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J102" s="3"/>
       <c r="K102" s="3"/>
     </row>
-    <row r="103">
+    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J103" s="3"/>
       <c r="K103" s="3"/>
     </row>
-    <row r="104">
+    <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J104" s="3"/>
       <c r="K104" s="3"/>
     </row>
-    <row r="105">
+    <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J105" s="3"/>
       <c r="K105" s="3"/>
     </row>
-    <row r="106">
+    <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J106" s="3"/>
       <c r="K106" s="3"/>
     </row>
-    <row r="107">
+    <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J107" s="3"/>
       <c r="K107" s="3"/>
     </row>
-    <row r="108">
+    <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J108" s="3"/>
       <c r="K108" s="3"/>
     </row>
-    <row r="109">
+    <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J109" s="3"/>
       <c r="K109" s="3"/>
     </row>
-    <row r="110">
+    <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J110" s="3"/>
       <c r="K110" s="3"/>
     </row>
-    <row r="111">
+    <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J111" s="3"/>
       <c r="K111" s="3"/>
     </row>
-    <row r="112">
+    <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J112" s="3"/>
       <c r="K112" s="3"/>
     </row>
-    <row r="113">
+    <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J113" s="3"/>
       <c r="K113" s="3"/>
     </row>
-    <row r="114">
+    <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J114" s="3"/>
       <c r="K114" s="3"/>
     </row>
-    <row r="115">
+    <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J115" s="3"/>
       <c r="K115" s="3"/>
     </row>
-    <row r="116">
+    <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J116" s="3"/>
       <c r="K116" s="3"/>
     </row>
-    <row r="117">
+    <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J117" s="3"/>
       <c r="K117" s="3"/>
     </row>
-    <row r="118">
+    <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J118" s="3"/>
       <c r="K118" s="3"/>
     </row>
-    <row r="119">
+    <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J119" s="3"/>
       <c r="K119" s="3"/>
     </row>
-    <row r="120">
+    <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J120" s="3"/>
       <c r="K120" s="3"/>
     </row>
-    <row r="121">
+    <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J121" s="3"/>
       <c r="K121" s="3"/>
     </row>
-    <row r="122">
+    <row r="122" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J122" s="3"/>
       <c r="K122" s="3"/>
     </row>
-    <row r="123">
+    <row r="123" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J123" s="3"/>
       <c r="K123" s="3"/>
     </row>
-    <row r="124">
+    <row r="124" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J124" s="3"/>
       <c r="K124" s="3"/>
     </row>
-    <row r="125">
+    <row r="125" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J125" s="3"/>
       <c r="K125" s="3"/>
     </row>
-    <row r="126">
+    <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J126" s="3"/>
       <c r="K126" s="3"/>
     </row>
-    <row r="127">
+    <row r="127" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J127" s="3"/>
       <c r="K127" s="3"/>
     </row>
-    <row r="128">
+    <row r="128" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J128" s="3"/>
       <c r="K128" s="3"/>
     </row>
-    <row r="129">
+    <row r="129" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J129" s="3"/>
       <c r="K129" s="3"/>
     </row>
-    <row r="130">
+    <row r="130" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J130" s="3"/>
       <c r="K130" s="3"/>
     </row>
-    <row r="131">
+    <row r="131" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J131" s="3"/>
       <c r="K131" s="3"/>
     </row>
-    <row r="132">
+    <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J132" s="3"/>
       <c r="K132" s="3"/>
     </row>
-    <row r="133">
+    <row r="133" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J133" s="3"/>
       <c r="K133" s="3"/>
     </row>
-    <row r="134">
+    <row r="134" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J134" s="3"/>
       <c r="K134" s="3"/>
     </row>
-    <row r="135">
+    <row r="135" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J135" s="3"/>
       <c r="K135" s="3"/>
     </row>
-    <row r="136">
+    <row r="136" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J136" s="3"/>
       <c r="K136" s="3"/>
     </row>
-    <row r="137">
+    <row r="137" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J137" s="3"/>
       <c r="K137" s="3"/>
     </row>
-    <row r="138">
+    <row r="138" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J138" s="3"/>
       <c r="K138" s="3"/>
     </row>
-    <row r="139">
+    <row r="139" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J139" s="3"/>
       <c r="K139" s="3"/>
     </row>
-    <row r="140">
+    <row r="140" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J140" s="3"/>
       <c r="K140" s="3"/>
     </row>
-    <row r="141">
+    <row r="141" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J141" s="3"/>
       <c r="K141" s="3"/>
     </row>
-    <row r="142">
+    <row r="142" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J142" s="3"/>
       <c r="K142" s="3"/>
     </row>
-    <row r="143">
+    <row r="143" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J143" s="3"/>
       <c r="K143" s="3"/>
     </row>
-    <row r="144">
+    <row r="144" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J144" s="3"/>
       <c r="K144" s="3"/>
     </row>
-    <row r="145">
+    <row r="145" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J145" s="3"/>
       <c r="K145" s="3"/>
     </row>
-    <row r="146">
+    <row r="146" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J146" s="3"/>
       <c r="K146" s="3"/>
     </row>
-    <row r="147">
+    <row r="147" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J147" s="3"/>
       <c r="K147" s="3"/>
     </row>
-    <row r="148">
+    <row r="148" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J148" s="3"/>
       <c r="K148" s="3"/>
     </row>
-    <row r="149">
+    <row r="149" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J149" s="3"/>
       <c r="K149" s="3"/>
     </row>
-    <row r="150">
+    <row r="150" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J150" s="3"/>
       <c r="K150" s="3"/>
     </row>
-    <row r="151">
+    <row r="151" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J151" s="3"/>
       <c r="K151" s="3"/>
     </row>
-    <row r="152">
+    <row r="152" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J152" s="3"/>
       <c r="K152" s="3"/>
     </row>
-    <row r="153">
+    <row r="153" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J153" s="3"/>
       <c r="K153" s="3"/>
     </row>
-    <row r="154">
+    <row r="154" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J154" s="3"/>
       <c r="K154" s="3"/>
     </row>
-    <row r="155">
+    <row r="155" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J155" s="3"/>
       <c r="K155" s="3"/>
     </row>
-    <row r="156">
+    <row r="156" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J156" s="3"/>
       <c r="K156" s="3"/>
     </row>
-    <row r="157">
+    <row r="157" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J157" s="3"/>
       <c r="K157" s="3"/>
     </row>
-    <row r="158">
+    <row r="158" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J158" s="3"/>
       <c r="K158" s="3"/>
     </row>
-    <row r="159">
+    <row r="159" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J159" s="3"/>
       <c r="K159" s="3"/>
     </row>
-    <row r="160">
+    <row r="160" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J160" s="3"/>
       <c r="K160" s="3"/>
     </row>
-    <row r="161">
+    <row r="161" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J161" s="3"/>
       <c r="K161" s="3"/>
     </row>
-    <row r="162">
+    <row r="162" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J162" s="3"/>
       <c r="K162" s="3"/>
     </row>
-    <row r="163">
+    <row r="163" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J163" s="3"/>
       <c r="K163" s="3"/>
     </row>
-    <row r="164">
+    <row r="164" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J164" s="3"/>
       <c r="K164" s="3"/>
     </row>
-    <row r="165">
+    <row r="165" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J165" s="3"/>
       <c r="K165" s="3"/>
     </row>
-    <row r="166">
+    <row r="166" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J166" s="3"/>
       <c r="K166" s="3"/>
     </row>
-    <row r="167">
+    <row r="167" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J167" s="3"/>
       <c r="K167" s="3"/>
     </row>
-    <row r="168">
+    <row r="168" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J168" s="3"/>
       <c r="K168" s="3"/>
     </row>
-    <row r="169">
+    <row r="169" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J169" s="3"/>
       <c r="K169" s="3"/>
     </row>
-    <row r="170">
+    <row r="170" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J170" s="3"/>
       <c r="K170" s="3"/>
     </row>
-    <row r="171">
+    <row r="171" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J171" s="3"/>
       <c r="K171" s="3"/>
     </row>
-    <row r="172">
+    <row r="172" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J172" s="3"/>
       <c r="K172" s="3"/>
     </row>
-    <row r="173">
+    <row r="173" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J173" s="3"/>
       <c r="K173" s="3"/>
     </row>
-    <row r="174">
+    <row r="174" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J174" s="3"/>
       <c r="K174" s="3"/>
     </row>
-    <row r="175">
+    <row r="175" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J175" s="3"/>
       <c r="K175" s="3"/>
     </row>
-    <row r="176">
+    <row r="176" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J176" s="3"/>
       <c r="K176" s="3"/>
     </row>
-    <row r="177">
+    <row r="177" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J177" s="3"/>
       <c r="K177" s="3"/>
     </row>
-    <row r="178">
+    <row r="178" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J178" s="3"/>
       <c r="K178" s="3"/>
     </row>
-    <row r="179">
+    <row r="179" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J179" s="3"/>
       <c r="K179" s="3"/>
     </row>
-    <row r="180">
+    <row r="180" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J180" s="3"/>
       <c r="K180" s="3"/>
     </row>
-    <row r="181">
+    <row r="181" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J181" s="3"/>
       <c r="K181" s="3"/>
     </row>
-    <row r="182">
+    <row r="182" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J182" s="3"/>
       <c r="K182" s="3"/>
     </row>
-    <row r="183">
+    <row r="183" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J183" s="3"/>
       <c r="K183" s="3"/>
     </row>
-    <row r="184">
+    <row r="184" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J184" s="3"/>
       <c r="K184" s="3"/>
     </row>
-    <row r="185">
+    <row r="185" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J185" s="3"/>
       <c r="K185" s="3"/>
     </row>
-    <row r="186">
+    <row r="186" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J186" s="3"/>
       <c r="K186" s="3"/>
     </row>
-    <row r="187">
+    <row r="187" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J187" s="3"/>
       <c r="K187" s="3"/>
     </row>
-    <row r="188">
+    <row r="188" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J188" s="3"/>
       <c r="K188" s="3"/>
     </row>
-    <row r="189">
+    <row r="189" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J189" s="3"/>
       <c r="K189" s="3"/>
     </row>
-    <row r="190">
+    <row r="190" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J190" s="3"/>
       <c r="K190" s="3"/>
     </row>
-    <row r="191">
+    <row r="191" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J191" s="3"/>
       <c r="K191" s="3"/>
     </row>
-    <row r="192">
+    <row r="192" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J192" s="3"/>
       <c r="K192" s="3"/>
     </row>
-    <row r="193">
+    <row r="193" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J193" s="3"/>
       <c r="K193" s="3"/>
     </row>
-    <row r="194">
+    <row r="194" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J194" s="3"/>
       <c r="K194" s="3"/>
     </row>
-    <row r="195">
+    <row r="195" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J195" s="3"/>
       <c r="K195" s="3"/>
     </row>
-    <row r="196">
+    <row r="196" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J196" s="3"/>
       <c r="K196" s="3"/>
     </row>
-    <row r="197">
+    <row r="197" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J197" s="3"/>
       <c r="K197" s="3"/>
     </row>
-    <row r="198">
+    <row r="198" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J198" s="3"/>
       <c r="K198" s="3"/>
     </row>
-    <row r="199">
+    <row r="199" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J199" s="3"/>
       <c r="K199" s="3"/>
     </row>
-    <row r="200">
+    <row r="200" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J200" s="3"/>
       <c r="K200" s="3"/>
     </row>
-    <row r="201">
+    <row r="201" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J201" s="3"/>
       <c r="K201" s="3"/>
     </row>
-    <row r="202">
+    <row r="202" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J202" s="3"/>
       <c r="K202" s="3"/>
     </row>
-    <row r="203">
+    <row r="203" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J203" s="3"/>
       <c r="K203" s="3"/>
     </row>
-    <row r="204">
+    <row r="204" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J204" s="3"/>
       <c r="K204" s="3"/>
     </row>
-    <row r="205">
+    <row r="205" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J205" s="3"/>
       <c r="K205" s="3"/>
     </row>
-    <row r="206">
+    <row r="206" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J206" s="3"/>
       <c r="K206" s="3"/>
     </row>
-    <row r="207">
+    <row r="207" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J207" s="3"/>
       <c r="K207" s="3"/>
     </row>
-    <row r="208">
+    <row r="208" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J208" s="3"/>
       <c r="K208" s="3"/>
     </row>
-    <row r="209">
+    <row r="209" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J209" s="3"/>
       <c r="K209" s="3"/>
     </row>
-    <row r="210">
+    <row r="210" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J210" s="3"/>
       <c r="K210" s="3"/>
     </row>
-    <row r="211">
+    <row r="211" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J211" s="3"/>
       <c r="K211" s="3"/>
     </row>
-    <row r="212">
+    <row r="212" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J212" s="3"/>
       <c r="K212" s="3"/>
     </row>
-    <row r="213">
+    <row r="213" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J213" s="3"/>
       <c r="K213" s="3"/>
     </row>
-    <row r="214">
+    <row r="214" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J214" s="3"/>
       <c r="K214" s="3"/>
     </row>
-    <row r="215">
+    <row r="215" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J215" s="3"/>
       <c r="K215" s="3"/>
     </row>
-    <row r="216">
+    <row r="216" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J216" s="3"/>
       <c r="K216" s="3"/>
     </row>
-    <row r="217">
+    <row r="217" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J217" s="3"/>
       <c r="K217" s="3"/>
     </row>
-    <row r="218">
+    <row r="218" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J218" s="3"/>
       <c r="K218" s="3"/>
     </row>
-    <row r="219">
+    <row r="219" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J219" s="3"/>
       <c r="K219" s="3"/>
     </row>
-    <row r="220">
+    <row r="220" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J220" s="3"/>
       <c r="K220" s="3"/>
     </row>
-    <row r="221">
+    <row r="221" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J221" s="3"/>
       <c r="K221" s="3"/>
     </row>
-    <row r="222">
+    <row r="222" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J222" s="3"/>
       <c r="K222" s="3"/>
     </row>
-    <row r="223">
+    <row r="223" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J223" s="3"/>
       <c r="K223" s="3"/>
     </row>
-    <row r="224">
+    <row r="224" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J224" s="3"/>
       <c r="K224" s="3"/>
     </row>
-    <row r="225">
+    <row r="225" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J225" s="3"/>
       <c r="K225" s="3"/>
     </row>
-    <row r="226">
+    <row r="226" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J226" s="3"/>
       <c r="K226" s="3"/>
     </row>
-    <row r="227">
+    <row r="227" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J227" s="3"/>
       <c r="K227" s="3"/>
     </row>
-    <row r="228">
+    <row r="228" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J228" s="3"/>
       <c r="K228" s="3"/>
     </row>
-    <row r="229">
+    <row r="229" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J229" s="3"/>
       <c r="K229" s="3"/>
     </row>
-    <row r="230">
+    <row r="230" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J230" s="3"/>
       <c r="K230" s="3"/>
     </row>
-    <row r="231">
+    <row r="231" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J231" s="3"/>
       <c r="K231" s="3"/>
     </row>
-    <row r="232">
+    <row r="232" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J232" s="3"/>
       <c r="K232" s="3"/>
     </row>
-    <row r="233">
+    <row r="233" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J233" s="3"/>
       <c r="K233" s="3"/>
     </row>
-    <row r="234">
+    <row r="234" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J234" s="3"/>
       <c r="K234" s="3"/>
     </row>
-    <row r="235">
+    <row r="235" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J235" s="3"/>
       <c r="K235" s="3"/>
     </row>
-    <row r="236">
+    <row r="236" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J236" s="3"/>
       <c r="K236" s="3"/>
     </row>
-    <row r="237">
+    <row r="237" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J237" s="3"/>
       <c r="K237" s="3"/>
     </row>
-    <row r="238">
+    <row r="238" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J238" s="3"/>
       <c r="K238" s="3"/>
     </row>
-    <row r="239">
+    <row r="239" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J239" s="3"/>
       <c r="K239" s="3"/>
     </row>
-    <row r="240">
+    <row r="240" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J240" s="3"/>
       <c r="K240" s="3"/>
     </row>
-    <row r="241">
+    <row r="241" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J241" s="3"/>
       <c r="K241" s="3"/>
     </row>
-    <row r="242">
+    <row r="242" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J242" s="3"/>
       <c r="K242" s="3"/>
     </row>
-    <row r="243">
+    <row r="243" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J243" s="3"/>
       <c r="K243" s="3"/>
     </row>
-    <row r="244">
+    <row r="244" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J244" s="3"/>
       <c r="K244" s="3"/>
     </row>
-    <row r="245">
+    <row r="245" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J245" s="3"/>
       <c r="K245" s="3"/>
     </row>
-    <row r="246">
+    <row r="246" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J246" s="3"/>
       <c r="K246" s="3"/>
     </row>
-    <row r="247">
+    <row r="247" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J247" s="3"/>
       <c r="K247" s="3"/>
     </row>
-    <row r="248">
+    <row r="248" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J248" s="3"/>
       <c r="K248" s="3"/>
     </row>
-    <row r="249">
+    <row r="249" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J249" s="3"/>
       <c r="K249" s="3"/>
     </row>
-    <row r="250">
+    <row r="250" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J250" s="3"/>
       <c r="K250" s="3"/>
     </row>
-    <row r="251">
+    <row r="251" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J251" s="3"/>
       <c r="K251" s="3"/>
     </row>
-    <row r="252">
+    <row r="252" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J252" s="3"/>
       <c r="K252" s="3"/>
     </row>
-    <row r="253">
+    <row r="253" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J253" s="3"/>
       <c r="K253" s="3"/>
     </row>
-    <row r="254">
+    <row r="254" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J254" s="3"/>
       <c r="K254" s="3"/>
     </row>
-    <row r="255">
+    <row r="255" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J255" s="3"/>
       <c r="K255" s="3"/>
     </row>
-    <row r="256">
+    <row r="256" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J256" s="3"/>
       <c r="K256" s="3"/>
     </row>
-    <row r="257">
+    <row r="257" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J257" s="3"/>
       <c r="K257" s="3"/>
     </row>
-    <row r="258">
+    <row r="258" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J258" s="3"/>
       <c r="K258" s="3"/>
     </row>
-    <row r="259">
+    <row r="259" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J259" s="3"/>
       <c r="K259" s="3"/>
     </row>
-    <row r="260">
+    <row r="260" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J260" s="3"/>
       <c r="K260" s="3"/>
     </row>
-    <row r="261">
+    <row r="261" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J261" s="3"/>
       <c r="K261" s="3"/>
     </row>
-    <row r="262">
+    <row r="262" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J262" s="3"/>
       <c r="K262" s="3"/>
     </row>
-    <row r="263">
+    <row r="263" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J263" s="3"/>
       <c r="K263" s="3"/>
     </row>
-    <row r="264">
+    <row r="264" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J264" s="3"/>
       <c r="K264" s="3"/>
     </row>
-    <row r="265">
+    <row r="265" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J265" s="3"/>
       <c r="K265" s="3"/>
     </row>
-    <row r="266">
+    <row r="266" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J266" s="3"/>
       <c r="K266" s="3"/>
     </row>
-    <row r="267">
+    <row r="267" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J267" s="3"/>
       <c r="K267" s="3"/>
     </row>
-    <row r="268">
+    <row r="268" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J268" s="3"/>
       <c r="K268" s="3"/>
     </row>
-    <row r="269">
+    <row r="269" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J269" s="3"/>
       <c r="K269" s="3"/>
     </row>
-    <row r="270">
+    <row r="270" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J270" s="3"/>
       <c r="K270" s="3"/>
     </row>
-    <row r="271">
+    <row r="271" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J271" s="3"/>
       <c r="K271" s="3"/>
     </row>
-    <row r="272">
+    <row r="272" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J272" s="3"/>
       <c r="K272" s="3"/>
     </row>
-    <row r="273">
+    <row r="273" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J273" s="3"/>
       <c r="K273" s="3"/>
     </row>
-    <row r="274">
+    <row r="274" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J274" s="3"/>
       <c r="K274" s="3"/>
     </row>
-    <row r="275">
+    <row r="275" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J275" s="3"/>
       <c r="K275" s="3"/>
     </row>
-    <row r="276">
+    <row r="276" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J276" s="3"/>
       <c r="K276" s="3"/>
     </row>
-    <row r="277">
+    <row r="277" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J277" s="3"/>
       <c r="K277" s="3"/>
     </row>
-    <row r="278">
+    <row r="278" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J278" s="3"/>
       <c r="K278" s="3"/>
     </row>
-    <row r="279">
+    <row r="279" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J279" s="3"/>
       <c r="K279" s="3"/>
     </row>
-    <row r="280">
+    <row r="280" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J280" s="3"/>
       <c r="K280" s="3"/>
     </row>
-    <row r="281">
+    <row r="281" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J281" s="3"/>
       <c r="K281" s="3"/>
     </row>
-    <row r="282">
+    <row r="282" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J282" s="3"/>
       <c r="K282" s="3"/>
     </row>
-    <row r="283">
+    <row r="283" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J283" s="3"/>
       <c r="K283" s="3"/>
     </row>
-    <row r="284">
+    <row r="284" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J284" s="3"/>
       <c r="K284" s="3"/>
     </row>
-    <row r="285">
+    <row r="285" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J285" s="3"/>
       <c r="K285" s="3"/>
     </row>
-    <row r="286">
+    <row r="286" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J286" s="3"/>
       <c r="K286" s="3"/>
     </row>
-    <row r="287">
+    <row r="287" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J287" s="3"/>
       <c r="K287" s="3"/>
     </row>
-    <row r="288">
+    <row r="288" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J288" s="3"/>
       <c r="K288" s="3"/>
     </row>
-    <row r="289">
+    <row r="289" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J289" s="3"/>
       <c r="K289" s="3"/>
     </row>
-    <row r="290">
+    <row r="290" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J290" s="3"/>
       <c r="K290" s="3"/>
     </row>
-    <row r="291">
+    <row r="291" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J291" s="3"/>
       <c r="K291" s="3"/>
     </row>
-    <row r="292">
+    <row r="292" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J292" s="3"/>
       <c r="K292" s="3"/>
     </row>
-    <row r="293">
+    <row r="293" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J293" s="3"/>
       <c r="K293" s="3"/>
     </row>
-    <row r="294">
+    <row r="294" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J294" s="3"/>
       <c r="K294" s="3"/>
     </row>
-    <row r="295">
+    <row r="295" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J295" s="3"/>
       <c r="K295" s="3"/>
     </row>
-    <row r="296">
+    <row r="296" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J296" s="3"/>
       <c r="K296" s="3"/>
     </row>
-    <row r="297">
+    <row r="297" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J297" s="3"/>
       <c r="K297" s="3"/>
     </row>
-    <row r="298">
+    <row r="298" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J298" s="3"/>
       <c r="K298" s="3"/>
     </row>
-    <row r="299">
+    <row r="299" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J299" s="3"/>
       <c r="K299" s="3"/>
     </row>
-    <row r="300">
+    <row r="300" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J300" s="3"/>
       <c r="K300" s="3"/>
     </row>
-    <row r="301">
+    <row r="301" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J301" s="3"/>
       <c r="K301" s="3"/>
     </row>
-    <row r="302">
+    <row r="302" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J302" s="3"/>
       <c r="K302" s="3"/>
     </row>
-    <row r="303">
+    <row r="303" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J303" s="3"/>
       <c r="K303" s="3"/>
     </row>
-    <row r="304">
+    <row r="304" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J304" s="3"/>
       <c r="K304" s="3"/>
     </row>
-    <row r="305">
+    <row r="305" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J305" s="3"/>
       <c r="K305" s="3"/>
     </row>
-    <row r="306">
+    <row r="306" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J306" s="3"/>
       <c r="K306" s="3"/>
     </row>
-    <row r="307">
+    <row r="307" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J307" s="3"/>
       <c r="K307" s="3"/>
     </row>
-    <row r="308">
+    <row r="308" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J308" s="3"/>
       <c r="K308" s="3"/>
     </row>
-    <row r="309">
+    <row r="309" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J309" s="3"/>
       <c r="K309" s="3"/>
     </row>
-    <row r="310">
+    <row r="310" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J310" s="3"/>
       <c r="K310" s="3"/>
     </row>
-    <row r="311">
+    <row r="311" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J311" s="3"/>
       <c r="K311" s="3"/>
     </row>
-    <row r="312">
+    <row r="312" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J312" s="3"/>
       <c r="K312" s="3"/>
     </row>
-    <row r="313">
+    <row r="313" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J313" s="3"/>
       <c r="K313" s="3"/>
     </row>
-    <row r="314">
+    <row r="314" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J314" s="3"/>
       <c r="K314" s="3"/>
     </row>
-    <row r="315">
+    <row r="315" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J315" s="3"/>
       <c r="K315" s="3"/>
     </row>
-    <row r="316">
+    <row r="316" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J316" s="3"/>
       <c r="K316" s="3"/>
     </row>
-    <row r="317">
+    <row r="317" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J317" s="3"/>
       <c r="K317" s="3"/>
     </row>
-    <row r="318">
+    <row r="318" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J318" s="3"/>
       <c r="K318" s="3"/>
     </row>
-    <row r="319">
+    <row r="319" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J319" s="3"/>
       <c r="K319" s="3"/>
     </row>
-    <row r="320">
+    <row r="320" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J320" s="3"/>
       <c r="K320" s="3"/>
     </row>
-    <row r="321">
+    <row r="321" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J321" s="3"/>
       <c r="K321" s="3"/>
     </row>
-    <row r="322">
+    <row r="322" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J322" s="3"/>
       <c r="K322" s="3"/>
     </row>
-    <row r="323">
+    <row r="323" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J323" s="3"/>
       <c r="K323" s="3"/>
     </row>
-    <row r="324">
+    <row r="324" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J324" s="3"/>
       <c r="K324" s="3"/>
     </row>
-    <row r="325">
+    <row r="325" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J325" s="3"/>
       <c r="K325" s="3"/>
     </row>
-    <row r="326">
+    <row r="326" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J326" s="3"/>
       <c r="K326" s="3"/>
     </row>
-    <row r="327">
+    <row r="327" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J327" s="3"/>
       <c r="K327" s="3"/>
     </row>
-    <row r="328">
+    <row r="328" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J328" s="3"/>
       <c r="K328" s="3"/>
     </row>
-    <row r="329">
+    <row r="329" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J329" s="3"/>
       <c r="K329" s="3"/>
     </row>
-    <row r="330">
+    <row r="330" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J330" s="3"/>
       <c r="K330" s="3"/>
     </row>
-    <row r="331">
+    <row r="331" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J331" s="3"/>
       <c r="K331" s="3"/>
     </row>
-    <row r="332">
+    <row r="332" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J332" s="3"/>
       <c r="K332" s="3"/>
     </row>
-    <row r="333">
+    <row r="333" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J333" s="3"/>
       <c r="K333" s="3"/>
     </row>
-    <row r="334">
+    <row r="334" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J334" s="3"/>
       <c r="K334" s="3"/>
     </row>
-    <row r="335">
+    <row r="335" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J335" s="3"/>
       <c r="K335" s="3"/>
     </row>
-    <row r="336">
+    <row r="336" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J336" s="3"/>
       <c r="K336" s="3"/>
     </row>
-    <row r="337">
+    <row r="337" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J337" s="3"/>
       <c r="K337" s="3"/>
     </row>
-    <row r="338">
+    <row r="338" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J338" s="3"/>
       <c r="K338" s="3"/>
     </row>
-    <row r="339">
+    <row r="339" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J339" s="3"/>
       <c r="K339" s="3"/>
     </row>
-    <row r="340">
+    <row r="340" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J340" s="3"/>
       <c r="K340" s="3"/>
     </row>
-    <row r="341">
+    <row r="341" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J341" s="3"/>
       <c r="K341" s="3"/>
     </row>
-    <row r="342">
+    <row r="342" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J342" s="3"/>
       <c r="K342" s="3"/>
     </row>
-    <row r="343">
+    <row r="343" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J343" s="3"/>
       <c r="K343" s="3"/>
     </row>
-    <row r="344">
+    <row r="344" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J344" s="3"/>
       <c r="K344" s="3"/>
     </row>
-    <row r="345">
+    <row r="345" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J345" s="3"/>
       <c r="K345" s="3"/>
     </row>
-    <row r="346">
+    <row r="346" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J346" s="3"/>
       <c r="K346" s="3"/>
     </row>
-    <row r="347">
+    <row r="347" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J347" s="3"/>
       <c r="K347" s="3"/>
     </row>
-    <row r="348">
+    <row r="348" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J348" s="3"/>
       <c r="K348" s="3"/>
     </row>
-    <row r="349">
+    <row r="349" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J349" s="3"/>
       <c r="K349" s="3"/>
     </row>
-    <row r="350">
+    <row r="350" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J350" s="3"/>
       <c r="K350" s="3"/>
     </row>
-    <row r="351">
+    <row r="351" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J351" s="3"/>
       <c r="K351" s="3"/>
     </row>
-    <row r="352">
+    <row r="352" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J352" s="3"/>
       <c r="K352" s="3"/>
     </row>
-    <row r="353">
+    <row r="353" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J353" s="3"/>
       <c r="K353" s="3"/>
     </row>
-    <row r="354">
+    <row r="354" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J354" s="3"/>
       <c r="K354" s="3"/>
     </row>
-    <row r="355">
+    <row r="355" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J355" s="3"/>
       <c r="K355" s="3"/>
     </row>
-    <row r="356">
+    <row r="356" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J356" s="3"/>
       <c r="K356" s="3"/>
     </row>
-    <row r="357">
+    <row r="357" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J357" s="3"/>
       <c r="K357" s="3"/>
     </row>
-    <row r="358">
+    <row r="358" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J358" s="3"/>
       <c r="K358" s="3"/>
     </row>
-    <row r="359">
+    <row r="359" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J359" s="3"/>
       <c r="K359" s="3"/>
     </row>
-    <row r="360">
+    <row r="360" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J360" s="3"/>
       <c r="K360" s="3"/>
     </row>
-    <row r="361">
+    <row r="361" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J361" s="3"/>
       <c r="K361" s="3"/>
     </row>
-    <row r="362">
+    <row r="362" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J362" s="3"/>
       <c r="K362" s="3"/>
     </row>
-    <row r="363">
+    <row r="363" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J363" s="3"/>
       <c r="K363" s="3"/>
     </row>
-    <row r="364">
+    <row r="364" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J364" s="3"/>
       <c r="K364" s="3"/>
     </row>
-    <row r="365">
+    <row r="365" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J365" s="3"/>
       <c r="K365" s="3"/>
     </row>
-    <row r="366">
+    <row r="366" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J366" s="3"/>
       <c r="K366" s="3"/>
     </row>
-    <row r="367">
+    <row r="367" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J367" s="3"/>
       <c r="K367" s="3"/>
     </row>
-    <row r="368">
+    <row r="368" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J368" s="3"/>
       <c r="K368" s="3"/>
     </row>
-    <row r="369">
+    <row r="369" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J369" s="3"/>
       <c r="K369" s="3"/>
     </row>
-    <row r="370">
+    <row r="370" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J370" s="3"/>
       <c r="K370" s="3"/>
     </row>
-    <row r="371">
+    <row r="371" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J371" s="3"/>
       <c r="K371" s="3"/>
     </row>
-    <row r="372">
+    <row r="372" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J372" s="3"/>
       <c r="K372" s="3"/>
     </row>
-    <row r="373">
+    <row r="373" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J373" s="3"/>
       <c r="K373" s="3"/>
     </row>
-    <row r="374">
+    <row r="374" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J374" s="3"/>
       <c r="K374" s="3"/>
     </row>
-    <row r="375">
+    <row r="375" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J375" s="3"/>
       <c r="K375" s="3"/>
     </row>
-    <row r="376">
+    <row r="376" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J376" s="3"/>
       <c r="K376" s="3"/>
     </row>
-    <row r="377">
+    <row r="377" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J377" s="3"/>
       <c r="K377" s="3"/>
     </row>
-    <row r="378">
+    <row r="378" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J378" s="3"/>
       <c r="K378" s="3"/>
     </row>
-    <row r="379">
+    <row r="379" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J379" s="3"/>
       <c r="K379" s="3"/>
     </row>
-    <row r="380">
+    <row r="380" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J380" s="3"/>
       <c r="K380" s="3"/>
     </row>
-    <row r="381">
+    <row r="381" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J381" s="3"/>
       <c r="K381" s="3"/>
     </row>
-    <row r="382">
+    <row r="382" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J382" s="3"/>
       <c r="K382" s="3"/>
     </row>
-    <row r="383">
+    <row r="383" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J383" s="3"/>
       <c r="K383" s="3"/>
     </row>
-    <row r="384">
+    <row r="384" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J384" s="3"/>
       <c r="K384" s="3"/>
     </row>
-    <row r="385">
+    <row r="385" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J385" s="3"/>
       <c r="K385" s="3"/>
     </row>
-    <row r="386">
+    <row r="386" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J386" s="3"/>
       <c r="K386" s="3"/>
     </row>
-    <row r="387">
+    <row r="387" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J387" s="3"/>
       <c r="K387" s="3"/>
     </row>
-    <row r="388">
+    <row r="388" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J388" s="3"/>
       <c r="K388" s="3"/>
     </row>
-    <row r="389">
+    <row r="389" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J389" s="3"/>
       <c r="K389" s="3"/>
     </row>
-    <row r="390">
+    <row r="390" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J390" s="3"/>
       <c r="K390" s="3"/>
     </row>
-    <row r="391">
+    <row r="391" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J391" s="3"/>
       <c r="K391" s="3"/>
     </row>
-    <row r="392">
+    <row r="392" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J392" s="3"/>
       <c r="K392" s="3"/>
     </row>
-    <row r="393">
+    <row r="393" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J393" s="3"/>
       <c r="K393" s="3"/>
     </row>
-    <row r="394">
+    <row r="394" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J394" s="3"/>
       <c r="K394" s="3"/>
     </row>
-    <row r="395">
+    <row r="395" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J395" s="3"/>
       <c r="K395" s="3"/>
     </row>
-    <row r="396">
+    <row r="396" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J396" s="3"/>
       <c r="K396" s="3"/>
     </row>
-    <row r="397">
+    <row r="397" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J397" s="3"/>
       <c r="K397" s="3"/>
     </row>
-    <row r="398">
+    <row r="398" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J398" s="3"/>
       <c r="K398" s="3"/>
     </row>
-    <row r="399">
+    <row r="399" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J399" s="3"/>
       <c r="K399" s="3"/>
     </row>
-    <row r="400">
+    <row r="400" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J400" s="3"/>
       <c r="K400" s="3"/>
     </row>
-    <row r="401">
+    <row r="401" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J401" s="3"/>
       <c r="K401" s="3"/>
     </row>
-    <row r="402">
+    <row r="402" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J402" s="3"/>
       <c r="K402" s="3"/>
     </row>
-    <row r="403">
+    <row r="403" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J403" s="3"/>
       <c r="K403" s="3"/>
     </row>
-    <row r="404">
+    <row r="404" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J404" s="3"/>
       <c r="K404" s="3"/>
     </row>
-    <row r="405">
+    <row r="405" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J405" s="3"/>
       <c r="K405" s="3"/>
     </row>
-    <row r="406">
+    <row r="406" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J406" s="3"/>
       <c r="K406" s="3"/>
     </row>
-    <row r="407">
+    <row r="407" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J407" s="3"/>
       <c r="K407" s="3"/>
     </row>
-    <row r="408">
+    <row r="408" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J408" s="3"/>
       <c r="K408" s="3"/>
     </row>
-    <row r="409">
+    <row r="409" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J409" s="3"/>
       <c r="K409" s="3"/>
     </row>
-    <row r="410">
+    <row r="410" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J410" s="3"/>
       <c r="K410" s="3"/>
     </row>
-    <row r="411">
+    <row r="411" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J411" s="3"/>
       <c r="K411" s="3"/>
     </row>
-    <row r="412">
+    <row r="412" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J412" s="3"/>
       <c r="K412" s="3"/>
     </row>
-    <row r="413">
+    <row r="413" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J413" s="3"/>
       <c r="K413" s="3"/>
     </row>
-    <row r="414">
+    <row r="414" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J414" s="3"/>
       <c r="K414" s="3"/>
     </row>
-    <row r="415">
+    <row r="415" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J415" s="3"/>
       <c r="K415" s="3"/>
     </row>
-    <row r="416">
+    <row r="416" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J416" s="3"/>
       <c r="K416" s="3"/>
     </row>
-    <row r="417">
+    <row r="417" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J417" s="3"/>
       <c r="K417" s="3"/>
     </row>
-    <row r="418">
+    <row r="418" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J418" s="3"/>
       <c r="K418" s="3"/>
     </row>
-    <row r="419">
+    <row r="419" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J419" s="3"/>
       <c r="K419" s="3"/>
     </row>
-    <row r="420">
+    <row r="420" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J420" s="3"/>
       <c r="K420" s="3"/>
     </row>
-    <row r="421">
+    <row r="421" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J421" s="3"/>
       <c r="K421" s="3"/>
     </row>
-    <row r="422">
+    <row r="422" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J422" s="3"/>
       <c r="K422" s="3"/>
     </row>
-    <row r="423">
+    <row r="423" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J423" s="3"/>
       <c r="K423" s="3"/>
     </row>
-    <row r="424">
+    <row r="424" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J424" s="3"/>
       <c r="K424" s="3"/>
     </row>
-    <row r="425">
+    <row r="425" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J425" s="3"/>
       <c r="K425" s="3"/>
     </row>
-    <row r="426">
+    <row r="426" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J426" s="3"/>
       <c r="K426" s="3"/>
     </row>
-    <row r="427">
+    <row r="427" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J427" s="3"/>
       <c r="K427" s="3"/>
     </row>
-    <row r="428">
+    <row r="428" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J428" s="3"/>
       <c r="K428" s="3"/>
     </row>
-    <row r="429">
+    <row r="429" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J429" s="3"/>
       <c r="K429" s="3"/>
     </row>
-    <row r="430">
+    <row r="430" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J430" s="3"/>
       <c r="K430" s="3"/>
     </row>
-    <row r="431">
+    <row r="431" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J431" s="3"/>
       <c r="K431" s="3"/>
     </row>
-    <row r="432">
+    <row r="432" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J432" s="3"/>
       <c r="K432" s="3"/>
     </row>
-    <row r="433">
+    <row r="433" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J433" s="3"/>
       <c r="K433" s="3"/>
     </row>
-    <row r="434">
+    <row r="434" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J434" s="3"/>
       <c r="K434" s="3"/>
     </row>
-    <row r="435">
+    <row r="435" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J435" s="3"/>
       <c r="K435" s="3"/>
     </row>
-    <row r="436">
+    <row r="436" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J436" s="3"/>
       <c r="K436" s="3"/>
     </row>
-    <row r="437">
+    <row r="437" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J437" s="3"/>
       <c r="K437" s="3"/>
     </row>
-    <row r="438">
+    <row r="438" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J438" s="3"/>
       <c r="K438" s="3"/>
     </row>
-    <row r="439">
+    <row r="439" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J439" s="3"/>
       <c r="K439" s="3"/>
     </row>
-    <row r="440">
+    <row r="440" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J440" s="3"/>
       <c r="K440" s="3"/>
     </row>
-    <row r="441">
+    <row r="441" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J441" s="3"/>
       <c r="K441" s="3"/>
     </row>
-    <row r="442">
+    <row r="442" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J442" s="3"/>
       <c r="K442" s="3"/>
     </row>
-    <row r="443">
+    <row r="443" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J443" s="3"/>
       <c r="K443" s="3"/>
     </row>
-    <row r="444">
+    <row r="444" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J444" s="3"/>
       <c r="K444" s="3"/>
     </row>
-    <row r="445">
+    <row r="445" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J445" s="3"/>
       <c r="K445" s="3"/>
     </row>
-    <row r="446">
+    <row r="446" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J446" s="3"/>
       <c r="K446" s="3"/>
     </row>
-    <row r="447">
+    <row r="447" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J447" s="3"/>
       <c r="K447" s="3"/>
     </row>
-    <row r="448">
+    <row r="448" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J448" s="3"/>
       <c r="K448" s="3"/>
     </row>
-    <row r="449">
+    <row r="449" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J449" s="3"/>
       <c r="K449" s="3"/>
     </row>
-    <row r="450">
+    <row r="450" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J450" s="3"/>
       <c r="K450" s="3"/>
     </row>
-    <row r="451">
+    <row r="451" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J451" s="3"/>
       <c r="K451" s="3"/>
     </row>
-    <row r="452">
+    <row r="452" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J452" s="3"/>
       <c r="K452" s="3"/>
     </row>
-    <row r="453">
+    <row r="453" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J453" s="3"/>
       <c r="K453" s="3"/>
     </row>
-    <row r="454">
+    <row r="454" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J454" s="3"/>
       <c r="K454" s="3"/>
     </row>
-    <row r="455">
+    <row r="455" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J455" s="3"/>
       <c r="K455" s="3"/>
     </row>
-    <row r="456">
+    <row r="456" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J456" s="3"/>
       <c r="K456" s="3"/>
     </row>
-    <row r="457">
+    <row r="457" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J457" s="3"/>
       <c r="K457" s="3"/>
     </row>
-    <row r="458">
+    <row r="458" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J458" s="3"/>
       <c r="K458" s="3"/>
     </row>
-    <row r="459">
+    <row r="459" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J459" s="3"/>
       <c r="K459" s="3"/>
     </row>
-    <row r="460">
+    <row r="460" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J460" s="3"/>
       <c r="K460" s="3"/>
     </row>
-    <row r="461">
+    <row r="461" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J461" s="3"/>
       <c r="K461" s="3"/>
     </row>
-    <row r="462">
+    <row r="462" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J462" s="3"/>
       <c r="K462" s="3"/>
     </row>
-    <row r="463">
+    <row r="463" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J463" s="3"/>
       <c r="K463" s="3"/>
     </row>
-    <row r="464">
+    <row r="464" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J464" s="3"/>
       <c r="K464" s="3"/>
     </row>
-    <row r="465">
+    <row r="465" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J465" s="3"/>
       <c r="K465" s="3"/>
     </row>
-    <row r="466">
+    <row r="466" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J466" s="3"/>
       <c r="K466" s="3"/>
     </row>
-    <row r="467">
+    <row r="467" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J467" s="3"/>
       <c r="K467" s="3"/>
     </row>
-    <row r="468">
+    <row r="468" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J468" s="3"/>
       <c r="K468" s="3"/>
     </row>
-    <row r="469">
+    <row r="469" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J469" s="3"/>
       <c r="K469" s="3"/>
     </row>
-    <row r="470">
+    <row r="470" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J470" s="3"/>
       <c r="K470" s="3"/>
     </row>
-    <row r="471">
+    <row r="471" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J471" s="3"/>
       <c r="K471" s="3"/>
     </row>
-    <row r="472">
+    <row r="472" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J472" s="3"/>
       <c r="K472" s="3"/>
     </row>
-    <row r="473">
+    <row r="473" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J473" s="3"/>
       <c r="K473" s="3"/>
     </row>
-    <row r="474">
+    <row r="474" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J474" s="3"/>
       <c r="K474" s="3"/>
     </row>
-    <row r="475">
+    <row r="475" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J475" s="3"/>
       <c r="K475" s="3"/>
     </row>
-    <row r="476">
+    <row r="476" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J476" s="3"/>
       <c r="K476" s="3"/>
     </row>
-    <row r="477">
+    <row r="477" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J477" s="3"/>
       <c r="K477" s="3"/>
     </row>
-    <row r="478">
+    <row r="478" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J478" s="3"/>
       <c r="K478" s="3"/>
     </row>
-    <row r="479">
+    <row r="479" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J479" s="3"/>
       <c r="K479" s="3"/>
     </row>
-    <row r="480">
+    <row r="480" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J480" s="3"/>
       <c r="K480" s="3"/>
     </row>
-    <row r="481">
+    <row r="481" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J481" s="3"/>
       <c r="K481" s="3"/>
     </row>
-    <row r="482">
+    <row r="482" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J482" s="3"/>
       <c r="K482" s="3"/>
     </row>
-    <row r="483">
+    <row r="483" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J483" s="3"/>
       <c r="K483" s="3"/>
     </row>
-    <row r="484">
+    <row r="484" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J484" s="3"/>
       <c r="K484" s="3"/>
     </row>
-    <row r="485">
+    <row r="485" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J485" s="3"/>
       <c r="K485" s="3"/>
     </row>
-    <row r="486">
+    <row r="486" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J486" s="3"/>
       <c r="K486" s="3"/>
     </row>
-    <row r="487">
+    <row r="487" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J487" s="3"/>
       <c r="K487" s="3"/>
     </row>
-    <row r="488">
+    <row r="488" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J488" s="3"/>
       <c r="K488" s="3"/>
     </row>
-    <row r="489">
+    <row r="489" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J489" s="3"/>
       <c r="K489" s="3"/>
     </row>
-    <row r="490">
+    <row r="490" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J490" s="3"/>
       <c r="K490" s="3"/>
     </row>
-    <row r="491">
+    <row r="491" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J491" s="3"/>
       <c r="K491" s="3"/>
     </row>
-    <row r="492">
+    <row r="492" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J492" s="3"/>
       <c r="K492" s="3"/>
     </row>
-    <row r="493">
+    <row r="493" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J493" s="3"/>
       <c r="K493" s="3"/>
     </row>
-    <row r="494">
+    <row r="494" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J494" s="3"/>
       <c r="K494" s="3"/>
     </row>
-    <row r="495">
+    <row r="495" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J495" s="3"/>
       <c r="K495" s="3"/>
     </row>
-    <row r="496">
+    <row r="496" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J496" s="3"/>
       <c r="K496" s="3"/>
     </row>
-    <row r="497">
+    <row r="497" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J497" s="3"/>
       <c r="K497" s="3"/>
     </row>
-    <row r="498">
+    <row r="498" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J498" s="3"/>
       <c r="K498" s="3"/>
     </row>
-    <row r="499">
+    <row r="499" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J499" s="3"/>
       <c r="K499" s="3"/>
     </row>
-    <row r="500">
+    <row r="500" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J500" s="3"/>
       <c r="K500" s="3"/>
     </row>
-    <row r="501">
+    <row r="501" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J501" s="3"/>
       <c r="K501" s="3"/>
     </row>
-    <row r="502">
+    <row r="502" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J502" s="3"/>
       <c r="K502" s="3"/>
     </row>
-    <row r="503">
+    <row r="503" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J503" s="3"/>
       <c r="K503" s="3"/>
     </row>
-    <row r="504">
+    <row r="504" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J504" s="3"/>
       <c r="K504" s="3"/>
     </row>
-    <row r="505">
+    <row r="505" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J505" s="3"/>
       <c r="K505" s="3"/>
     </row>
-    <row r="506">
+    <row r="506" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J506" s="3"/>
       <c r="K506" s="3"/>
     </row>
-    <row r="507">
+    <row r="507" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J507" s="3"/>
       <c r="K507" s="3"/>
     </row>
-    <row r="508">
+    <row r="508" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J508" s="3"/>
       <c r="K508" s="3"/>
     </row>
-    <row r="509">
+    <row r="509" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J509" s="3"/>
       <c r="K509" s="3"/>
     </row>
-    <row r="510">
+    <row r="510" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J510" s="3"/>
       <c r="K510" s="3"/>
     </row>
-    <row r="511">
+    <row r="511" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J511" s="3"/>
       <c r="K511" s="3"/>
     </row>
-    <row r="512">
+    <row r="512" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J512" s="3"/>
       <c r="K512" s="3"/>
     </row>
-    <row r="513">
+    <row r="513" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J513" s="3"/>
       <c r="K513" s="3"/>
     </row>
-    <row r="514">
+    <row r="514" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J514" s="3"/>
       <c r="K514" s="3"/>
     </row>
-    <row r="515">
+    <row r="515" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J515" s="3"/>
       <c r="K515" s="3"/>
     </row>
-    <row r="516">
+    <row r="516" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J516" s="3"/>
       <c r="K516" s="3"/>
     </row>
-    <row r="517">
+    <row r="517" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J517" s="3"/>
       <c r="K517" s="3"/>
     </row>
-    <row r="518">
+    <row r="518" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J518" s="3"/>
       <c r="K518" s="3"/>
     </row>
-    <row r="519">
+    <row r="519" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J519" s="3"/>
       <c r="K519" s="3"/>
     </row>
-    <row r="520">
+    <row r="520" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J520" s="3"/>
       <c r="K520" s="3"/>
     </row>
-    <row r="521">
+    <row r="521" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J521" s="3"/>
       <c r="K521" s="3"/>
     </row>
-    <row r="522">
+    <row r="522" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J522" s="3"/>
       <c r="K522" s="3"/>
     </row>
-    <row r="523">
+    <row r="523" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J523" s="3"/>
       <c r="K523" s="3"/>
     </row>
-    <row r="524">
+    <row r="524" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J524" s="3"/>
       <c r="K524" s="3"/>
     </row>
-    <row r="525">
+    <row r="525" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J525" s="3"/>
       <c r="K525" s="3"/>
     </row>
-    <row r="526">
+    <row r="526" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J526" s="3"/>
       <c r="K526" s="3"/>
     </row>
-    <row r="527">
+    <row r="527" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J527" s="3"/>
       <c r="K527" s="3"/>
     </row>
-    <row r="528">
+    <row r="528" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J528" s="3"/>
       <c r="K528" s="3"/>
     </row>
-    <row r="529">
+    <row r="529" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J529" s="3"/>
       <c r="K529" s="3"/>
     </row>
-    <row r="530">
+    <row r="530" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J530" s="3"/>
       <c r="K530" s="3"/>
     </row>
-    <row r="531">
+    <row r="531" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J531" s="3"/>
       <c r="K531" s="3"/>
     </row>
-    <row r="532">
+    <row r="532" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J532" s="3"/>
       <c r="K532" s="3"/>
     </row>
-    <row r="533">
+    <row r="533" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J533" s="3"/>
       <c r="K533" s="3"/>
     </row>
-    <row r="534">
+    <row r="534" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J534" s="3"/>
       <c r="K534" s="3"/>
     </row>
-    <row r="535">
+    <row r="535" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J535" s="3"/>
       <c r="K535" s="3"/>
     </row>
-    <row r="536">
+    <row r="536" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J536" s="3"/>
       <c r="K536" s="3"/>
     </row>
-    <row r="537">
+    <row r="537" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J537" s="3"/>
       <c r="K537" s="3"/>
     </row>
-    <row r="538">
+    <row r="538" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J538" s="3"/>
       <c r="K538" s="3"/>
     </row>
-    <row r="539">
+    <row r="539" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J539" s="3"/>
       <c r="K539" s="3"/>
     </row>
-    <row r="540">
+    <row r="540" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J540" s="3"/>
       <c r="K540" s="3"/>
     </row>
-    <row r="541">
+    <row r="541" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J541" s="3"/>
       <c r="K541" s="3"/>
     </row>
-    <row r="542">
+    <row r="542" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J542" s="3"/>
       <c r="K542" s="3"/>
     </row>
-    <row r="543">
+    <row r="543" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J543" s="3"/>
       <c r="K543" s="3"/>
     </row>
-    <row r="544">
+    <row r="544" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J544" s="3"/>
       <c r="K544" s="3"/>
     </row>
-    <row r="545">
+    <row r="545" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J545" s="3"/>
       <c r="K545" s="3"/>
     </row>
-    <row r="546">
+    <row r="546" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J546" s="3"/>
       <c r="K546" s="3"/>
     </row>
-    <row r="547">
+    <row r="547" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J547" s="3"/>
       <c r="K547" s="3"/>
     </row>
-    <row r="548">
+    <row r="548" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J548" s="3"/>
       <c r="K548" s="3"/>
     </row>
-    <row r="549">
+    <row r="549" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J549" s="3"/>
       <c r="K549" s="3"/>
     </row>
-    <row r="550">
+    <row r="550" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J550" s="3"/>
       <c r="K550" s="3"/>
     </row>
-    <row r="551">
+    <row r="551" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J551" s="3"/>
       <c r="K551" s="3"/>
     </row>
-    <row r="552">
+    <row r="552" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J552" s="3"/>
       <c r="K552" s="3"/>
     </row>
-    <row r="553">
+    <row r="553" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J553" s="3"/>
       <c r="K553" s="3"/>
     </row>
-    <row r="554">
+    <row r="554" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J554" s="3"/>
       <c r="K554" s="3"/>
     </row>
-    <row r="555">
+    <row r="555" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J555" s="3"/>
       <c r="K555" s="3"/>
     </row>
-    <row r="556">
+    <row r="556" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J556" s="3"/>
       <c r="K556" s="3"/>
     </row>
-    <row r="557">
+    <row r="557" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J557" s="3"/>
       <c r="K557" s="3"/>
     </row>
-    <row r="558">
+    <row r="558" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J558" s="3"/>
       <c r="K558" s="3"/>
     </row>
-    <row r="559">
+    <row r="559" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J559" s="3"/>
       <c r="K559" s="3"/>
     </row>
-    <row r="560">
+    <row r="560" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J560" s="3"/>
       <c r="K560" s="3"/>
     </row>
-    <row r="561">
+    <row r="561" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J561" s="3"/>
       <c r="K561" s="3"/>
     </row>
-    <row r="562">
+    <row r="562" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J562" s="3"/>
       <c r="K562" s="3"/>
     </row>
-    <row r="563">
+    <row r="563" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J563" s="3"/>
       <c r="K563" s="3"/>
     </row>
-    <row r="564">
+    <row r="564" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J564" s="3"/>
       <c r="K564" s="3"/>
     </row>
-    <row r="565">
+    <row r="565" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J565" s="3"/>
       <c r="K565" s="3"/>
     </row>
-    <row r="566">
+    <row r="566" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J566" s="3"/>
       <c r="K566" s="3"/>
     </row>
-    <row r="567">
+    <row r="567" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J567" s="3"/>
       <c r="K567" s="3"/>
     </row>
-    <row r="568">
+    <row r="568" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J568" s="3"/>
       <c r="K568" s="3"/>
     </row>
-    <row r="569">
+    <row r="569" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J569" s="3"/>
       <c r="K569" s="3"/>
     </row>
-    <row r="570">
+    <row r="570" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J570" s="3"/>
       <c r="K570" s="3"/>
     </row>
-    <row r="571">
+    <row r="571" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J571" s="3"/>
       <c r="K571" s="3"/>
     </row>
-    <row r="572">
+    <row r="572" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J572" s="3"/>
       <c r="K572" s="3"/>
     </row>
-    <row r="573">
+    <row r="573" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J573" s="3"/>
       <c r="K573" s="3"/>
     </row>
-    <row r="574">
+    <row r="574" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J574" s="3"/>
       <c r="K574" s="3"/>
     </row>
-    <row r="575">
+    <row r="575" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J575" s="3"/>
       <c r="K575" s="3"/>
     </row>
-    <row r="576">
+    <row r="576" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J576" s="3"/>
       <c r="K576" s="3"/>
     </row>
-    <row r="577">
+    <row r="577" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J577" s="3"/>
       <c r="K577" s="3"/>
     </row>
-    <row r="578">
+    <row r="578" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J578" s="3"/>
       <c r="K578" s="3"/>
     </row>
-    <row r="579">
+    <row r="579" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J579" s="3"/>
       <c r="K579" s="3"/>
     </row>
-    <row r="580">
+    <row r="580" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J580" s="3"/>
       <c r="K580" s="3"/>
     </row>
-    <row r="581">
+    <row r="581" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J581" s="3"/>
       <c r="K581" s="3"/>
     </row>
-    <row r="582">
+    <row r="582" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J582" s="3"/>
       <c r="K582" s="3"/>
     </row>
-    <row r="583">
+    <row r="583" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J583" s="3"/>
       <c r="K583" s="3"/>
     </row>
-    <row r="584">
+    <row r="584" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J584" s="3"/>
       <c r="K584" s="3"/>
     </row>
-    <row r="585">
+    <row r="585" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J585" s="3"/>
       <c r="K585" s="3"/>
     </row>
-    <row r="586">
+    <row r="586" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J586" s="3"/>
       <c r="K586" s="3"/>
     </row>
-    <row r="587">
+    <row r="587" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J587" s="3"/>
       <c r="K587" s="3"/>
     </row>
-    <row r="588">
+    <row r="588" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J588" s="3"/>
       <c r="K588" s="3"/>
     </row>
-    <row r="589">
+    <row r="589" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J589" s="3"/>
       <c r="K589" s="3"/>
     </row>
-    <row r="590">
+    <row r="590" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J590" s="3"/>
       <c r="K590" s="3"/>
     </row>
-    <row r="591">
+    <row r="591" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J591" s="3"/>
       <c r="K591" s="3"/>
     </row>
-    <row r="592">
+    <row r="592" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J592" s="3"/>
       <c r="K592" s="3"/>
     </row>
-    <row r="593">
+    <row r="593" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J593" s="3"/>
       <c r="K593" s="3"/>
     </row>
-    <row r="594">
+    <row r="594" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J594" s="3"/>
       <c r="K594" s="3"/>
     </row>
-    <row r="595">
+    <row r="595" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J595" s="3"/>
       <c r="K595" s="3"/>
     </row>
-    <row r="596">
+    <row r="596" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J596" s="3"/>
       <c r="K596" s="3"/>
     </row>
-    <row r="597">
+    <row r="597" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J597" s="3"/>
       <c r="K597" s="3"/>
     </row>
-    <row r="598">
+    <row r="598" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J598" s="3"/>
       <c r="K598" s="3"/>
     </row>
-    <row r="599">
+    <row r="599" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J599" s="3"/>
       <c r="K599" s="3"/>
     </row>
-    <row r="600">
+    <row r="600" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J600" s="3"/>
       <c r="K600" s="3"/>
     </row>
-    <row r="601">
+    <row r="601" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J601" s="3"/>
       <c r="K601" s="3"/>
     </row>
-    <row r="602">
+    <row r="602" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J602" s="3"/>
       <c r="K602" s="3"/>
     </row>
-    <row r="603">
+    <row r="603" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J603" s="3"/>
       <c r="K603" s="3"/>
     </row>
-    <row r="604">
+    <row r="604" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J604" s="3"/>
       <c r="K604" s="3"/>
     </row>
-    <row r="605">
+    <row r="605" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J605" s="3"/>
       <c r="K605" s="3"/>
     </row>
-    <row r="606">
+    <row r="606" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J606" s="3"/>
       <c r="K606" s="3"/>
     </row>
-    <row r="607">
+    <row r="607" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J607" s="3"/>
       <c r="K607" s="3"/>
     </row>
-    <row r="608">
+    <row r="608" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J608" s="3"/>
       <c r="K608" s="3"/>
     </row>
-    <row r="609">
+    <row r="609" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J609" s="3"/>
       <c r="K609" s="3"/>
     </row>
-    <row r="610">
+    <row r="610" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J610" s="3"/>
       <c r="K610" s="3"/>
     </row>
-    <row r="611">
+    <row r="611" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J611" s="3"/>
       <c r="K611" s="3"/>
     </row>
-    <row r="612">
+    <row r="612" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J612" s="3"/>
       <c r="K612" s="3"/>
     </row>
-    <row r="613">
+    <row r="613" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J613" s="3"/>
       <c r="K613" s="3"/>
     </row>
-    <row r="614">
+    <row r="614" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J614" s="3"/>
       <c r="K614" s="3"/>
     </row>
-    <row r="615">
+    <row r="615" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J615" s="3"/>
       <c r="K615" s="3"/>
     </row>
-    <row r="616">
+    <row r="616" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J616" s="3"/>
       <c r="K616" s="3"/>
     </row>
-    <row r="617">
+    <row r="617" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J617" s="3"/>
       <c r="K617" s="3"/>
     </row>
-    <row r="618">
+    <row r="618" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J618" s="3"/>
       <c r="K618" s="3"/>
     </row>
-    <row r="619">
+    <row r="619" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J619" s="3"/>
       <c r="K619" s="3"/>
     </row>
-    <row r="620">
+    <row r="620" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J620" s="3"/>
       <c r="K620" s="3"/>
     </row>
-    <row r="621">
+    <row r="621" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J621" s="3"/>
       <c r="K621" s="3"/>
     </row>
-    <row r="622">
+    <row r="622" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J622" s="3"/>
       <c r="K622" s="3"/>
     </row>
-    <row r="623">
+    <row r="623" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J623" s="3"/>
       <c r="K623" s="3"/>
     </row>
-    <row r="624">
+    <row r="624" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J624" s="3"/>
       <c r="K624" s="3"/>
     </row>
-    <row r="625">
+    <row r="625" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J625" s="3"/>
       <c r="K625" s="3"/>
     </row>
-    <row r="626">
+    <row r="626" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J626" s="3"/>
       <c r="K626" s="3"/>
     </row>
-    <row r="627">
+    <row r="627" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J627" s="3"/>
       <c r="K627" s="3"/>
     </row>
-    <row r="628">
+    <row r="628" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J628" s="3"/>
       <c r="K628" s="3"/>
     </row>
-    <row r="629">
+    <row r="629" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J629" s="3"/>
       <c r="K629" s="3"/>
     </row>
-    <row r="630">
+    <row r="630" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J630" s="3"/>
       <c r="K630" s="3"/>
     </row>
-    <row r="631">
+    <row r="631" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J631" s="3"/>
       <c r="K631" s="3"/>
     </row>
-    <row r="632">
+    <row r="632" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J632" s="3"/>
       <c r="K632" s="3"/>
     </row>
-    <row r="633">
+    <row r="633" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J633" s="3"/>
       <c r="K633" s="3"/>
     </row>
-    <row r="634">
+    <row r="634" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J634" s="3"/>
       <c r="K634" s="3"/>
     </row>
-    <row r="635">
+    <row r="635" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J635" s="3"/>
       <c r="K635" s="3"/>
     </row>
-    <row r="636">
+    <row r="636" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J636" s="3"/>
       <c r="K636" s="3"/>
     </row>
-    <row r="637">
+    <row r="637" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J637" s="3"/>
       <c r="K637" s="3"/>
     </row>
-    <row r="638">
+    <row r="638" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J638" s="3"/>
       <c r="K638" s="3"/>
     </row>
-    <row r="639">
+    <row r="639" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J639" s="3"/>
       <c r="K639" s="3"/>
     </row>
-    <row r="640">
+    <row r="640" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J640" s="3"/>
       <c r="K640" s="3"/>
     </row>
-    <row r="641">
+    <row r="641" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J641" s="3"/>
       <c r="K641" s="3"/>
     </row>
-    <row r="642">
+    <row r="642" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J642" s="3"/>
       <c r="K642" s="3"/>
     </row>
-    <row r="643">
+    <row r="643" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J643" s="3"/>
       <c r="K643" s="3"/>
     </row>
-    <row r="644">
+    <row r="644" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J644" s="3"/>
       <c r="K644" s="3"/>
     </row>
-    <row r="645">
+    <row r="645" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J645" s="3"/>
       <c r="K645" s="3"/>
     </row>
-    <row r="646">
+    <row r="646" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J646" s="3"/>
       <c r="K646" s="3"/>
     </row>
-    <row r="647">
+    <row r="647" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J647" s="3"/>
       <c r="K647" s="3"/>
     </row>
-    <row r="648">
+    <row r="648" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J648" s="3"/>
       <c r="K648" s="3"/>
     </row>
-    <row r="649">
+    <row r="649" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J649" s="3"/>
       <c r="K649" s="3"/>
     </row>
-    <row r="650">
+    <row r="650" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J650" s="3"/>
       <c r="K650" s="3"/>
     </row>
-    <row r="651">
+    <row r="651" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J651" s="3"/>
       <c r="K651" s="3"/>
     </row>
-    <row r="652">
+    <row r="652" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J652" s="3"/>
       <c r="K652" s="3"/>
     </row>
-    <row r="653">
+    <row r="653" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J653" s="3"/>
       <c r="K653" s="3"/>
     </row>
-    <row r="654">
+    <row r="654" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J654" s="3"/>
       <c r="K654" s="3"/>
     </row>
-    <row r="655">
+    <row r="655" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J655" s="3"/>
       <c r="K655" s="3"/>
     </row>
-    <row r="656">
+    <row r="656" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J656" s="3"/>
       <c r="K656" s="3"/>
     </row>
-    <row r="657">
+    <row r="657" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J657" s="3"/>
       <c r="K657" s="3"/>
     </row>
-    <row r="658">
+    <row r="658" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J658" s="3"/>
       <c r="K658" s="3"/>
     </row>
-    <row r="659">
+    <row r="659" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J659" s="3"/>
       <c r="K659" s="3"/>
     </row>
-    <row r="660">
+    <row r="660" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J660" s="3"/>
       <c r="K660" s="3"/>
     </row>
-    <row r="661">
+    <row r="661" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J661" s="3"/>
       <c r="K661" s="3"/>
     </row>
-    <row r="662">
+    <row r="662" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J662" s="3"/>
       <c r="K662" s="3"/>
     </row>
-    <row r="663">
+    <row r="663" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J663" s="3"/>
       <c r="K663" s="3"/>
     </row>
-    <row r="664">
+    <row r="664" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J664" s="3"/>
       <c r="K664" s="3"/>
     </row>
-    <row r="665">
+    <row r="665" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J665" s="3"/>
       <c r="K665" s="3"/>
     </row>
-    <row r="666">
+    <row r="666" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J666" s="3"/>
       <c r="K666" s="3"/>
     </row>
-    <row r="667">
+    <row r="667" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J667" s="3"/>
       <c r="K667" s="3"/>
     </row>
-    <row r="668">
+    <row r="668" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J668" s="3"/>
       <c r="K668" s="3"/>
     </row>
-    <row r="669">
+    <row r="669" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J669" s="3"/>
       <c r="K669" s="3"/>
     </row>
-    <row r="670">
+    <row r="670" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J670" s="3"/>
       <c r="K670" s="3"/>
     </row>
-    <row r="671">
+    <row r="671" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J671" s="3"/>
       <c r="K671" s="3"/>
     </row>
-    <row r="672">
+    <row r="672" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J672" s="3"/>
       <c r="K672" s="3"/>
     </row>
-    <row r="673">
+    <row r="673" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J673" s="3"/>
       <c r="K673" s="3"/>
     </row>
-    <row r="674">
+    <row r="674" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J674" s="3"/>
       <c r="K674" s="3"/>
     </row>
-    <row r="675">
+    <row r="675" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J675" s="3"/>
       <c r="K675" s="3"/>
     </row>
-    <row r="676">
+    <row r="676" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J676" s="3"/>
       <c r="K676" s="3"/>
     </row>
-    <row r="677">
+    <row r="677" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J677" s="3"/>
       <c r="K677" s="3"/>
     </row>
-    <row r="678">
+    <row r="678" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J678" s="3"/>
       <c r="K678" s="3"/>
     </row>
-    <row r="679">
+    <row r="679" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J679" s="3"/>
       <c r="K679" s="3"/>
     </row>
-    <row r="680">
+    <row r="680" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J680" s="3"/>
       <c r="K680" s="3"/>
     </row>
-    <row r="681">
+    <row r="681" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J681" s="3"/>
       <c r="K681" s="3"/>
     </row>
-    <row r="682">
+    <row r="682" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J682" s="3"/>
       <c r="K682" s="3"/>
     </row>
-    <row r="683">
+    <row r="683" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J683" s="3"/>
       <c r="K683" s="3"/>
     </row>
-    <row r="684">
+    <row r="684" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J684" s="3"/>
       <c r="K684" s="3"/>
     </row>
-    <row r="685">
+    <row r="685" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J685" s="3"/>
       <c r="K685" s="3"/>
     </row>
-    <row r="686">
+    <row r="686" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J686" s="3"/>
       <c r="K686" s="3"/>
     </row>
-    <row r="687">
+    <row r="687" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J687" s="3"/>
       <c r="K687" s="3"/>
     </row>
-    <row r="688">
+    <row r="688" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J688" s="3"/>
       <c r="K688" s="3"/>
     </row>
-    <row r="689">
+    <row r="689" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J689" s="3"/>
       <c r="K689" s="3"/>
     </row>
-    <row r="690">
+    <row r="690" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J690" s="3"/>
       <c r="K690" s="3"/>
     </row>
-    <row r="691">
+    <row r="691" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J691" s="3"/>
       <c r="K691" s="3"/>
     </row>
-    <row r="692">
+    <row r="692" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J692" s="3"/>
       <c r="K692" s="3"/>
     </row>
-    <row r="693">
+    <row r="693" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J693" s="3"/>
       <c r="K693" s="3"/>
     </row>
-    <row r="694">
+    <row r="694" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J694" s="3"/>
       <c r="K694" s="3"/>
     </row>
-    <row r="695">
+    <row r="695" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J695" s="3"/>
       <c r="K695" s="3"/>
     </row>
-    <row r="696">
+    <row r="696" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J696" s="3"/>
       <c r="K696" s="3"/>
     </row>
-    <row r="697">
+    <row r="697" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J697" s="3"/>
       <c r="K697" s="3"/>
     </row>
-    <row r="698">
+    <row r="698" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J698" s="3"/>
       <c r="K698" s="3"/>
     </row>
-    <row r="699">
+    <row r="699" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J699" s="3"/>
       <c r="K699" s="3"/>
     </row>
-    <row r="700">
+    <row r="700" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J700" s="3"/>
       <c r="K700" s="3"/>
     </row>
-    <row r="701">
+    <row r="701" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J701" s="3"/>
       <c r="K701" s="3"/>
     </row>
-    <row r="702">
+    <row r="702" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J702" s="3"/>
       <c r="K702" s="3"/>
     </row>
-    <row r="703">
+    <row r="703" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J703" s="3"/>
       <c r="K703" s="3"/>
     </row>
-    <row r="704">
+    <row r="704" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J704" s="3"/>
       <c r="K704" s="3"/>
     </row>
-    <row r="705">
+    <row r="705" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J705" s="3"/>
       <c r="K705" s="3"/>
     </row>
-    <row r="706">
+    <row r="706" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J706" s="3"/>
       <c r="K706" s="3"/>
     </row>
-    <row r="707">
+    <row r="707" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J707" s="3"/>
       <c r="K707" s="3"/>
     </row>
-    <row r="708">
+    <row r="708" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J708" s="3"/>
       <c r="K708" s="3"/>
     </row>
-    <row r="709">
+    <row r="709" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J709" s="3"/>
       <c r="K709" s="3"/>
     </row>
-    <row r="710">
+    <row r="710" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J710" s="3"/>
       <c r="K710" s="3"/>
     </row>
-    <row r="711">
+    <row r="711" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J711" s="3"/>
       <c r="K711" s="3"/>
     </row>
-    <row r="712">
+    <row r="712" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J712" s="3"/>
       <c r="K712" s="3"/>
     </row>
-    <row r="713">
+    <row r="713" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J713" s="3"/>
       <c r="K713" s="3"/>
     </row>
-    <row r="714">
+    <row r="714" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J714" s="3"/>
       <c r="K714" s="3"/>
     </row>
-    <row r="715">
+    <row r="715" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J715" s="3"/>
       <c r="K715" s="3"/>
     </row>
-    <row r="716">
+    <row r="716" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J716" s="3"/>
       <c r="K716" s="3"/>
     </row>
-    <row r="717">
+    <row r="717" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J717" s="3"/>
       <c r="K717" s="3"/>
     </row>
-    <row r="718">
+    <row r="718" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J718" s="3"/>
       <c r="K718" s="3"/>
     </row>
-    <row r="719">
+    <row r="719" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J719" s="3"/>
       <c r="K719" s="3"/>
     </row>
-    <row r="720">
+    <row r="720" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J720" s="3"/>
       <c r="K720" s="3"/>
     </row>
-    <row r="721">
+    <row r="721" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J721" s="3"/>
       <c r="K721" s="3"/>
     </row>
-    <row r="722">
+    <row r="722" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J722" s="3"/>
       <c r="K722" s="3"/>
     </row>
-    <row r="723">
+    <row r="723" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J723" s="3"/>
       <c r="K723" s="3"/>
     </row>
-    <row r="724">
+    <row r="724" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J724" s="3"/>
       <c r="K724" s="3"/>
     </row>
-    <row r="725">
+    <row r="725" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J725" s="3"/>
       <c r="K725" s="3"/>
     </row>
-    <row r="726">
+    <row r="726" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J726" s="3"/>
       <c r="K726" s="3"/>
     </row>
-    <row r="727">
+    <row r="727" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J727" s="3"/>
       <c r="K727" s="3"/>
     </row>
-    <row r="728">
+    <row r="728" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J728" s="3"/>
       <c r="K728" s="3"/>
     </row>
-    <row r="729">
+    <row r="729" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J729" s="3"/>
       <c r="K729" s="3"/>
     </row>
-    <row r="730">
+    <row r="730" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J730" s="3"/>
       <c r="K730" s="3"/>
     </row>
-    <row r="731">
+    <row r="731" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J731" s="3"/>
       <c r="K731" s="3"/>
     </row>
-    <row r="732">
+    <row r="732" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J732" s="3"/>
       <c r="K732" s="3"/>
     </row>
-    <row r="733">
+    <row r="733" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J733" s="3"/>
       <c r="K733" s="3"/>
     </row>
-    <row r="734">
+    <row r="734" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J734" s="3"/>
       <c r="K734" s="3"/>
     </row>
-    <row r="735">
+    <row r="735" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J735" s="3"/>
       <c r="K735" s="3"/>
     </row>
-    <row r="736">
+    <row r="736" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J736" s="3"/>
       <c r="K736" s="3"/>
     </row>
-    <row r="737">
+    <row r="737" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J737" s="3"/>
       <c r="K737" s="3"/>
     </row>
-    <row r="738">
+    <row r="738" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J738" s="3"/>
       <c r="K738" s="3"/>
     </row>
-    <row r="739">
+    <row r="739" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J739" s="3"/>
       <c r="K739" s="3"/>
     </row>
-    <row r="740">
+    <row r="740" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J740" s="3"/>
       <c r="K740" s="3"/>
     </row>
-    <row r="741">
+    <row r="741" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J741" s="3"/>
       <c r="K741" s="3"/>
     </row>
-    <row r="742">
+    <row r="742" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J742" s="3"/>
       <c r="K742" s="3"/>
     </row>
-    <row r="743">
+    <row r="743" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J743" s="3"/>
       <c r="K743" s="3"/>
     </row>
-    <row r="744">
+    <row r="744" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J744" s="3"/>
       <c r="K744" s="3"/>
     </row>
-    <row r="745">
+    <row r="745" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J745" s="3"/>
       <c r="K745" s="3"/>
     </row>
-    <row r="746">
+    <row r="746" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J746" s="3"/>
       <c r="K746" s="3"/>
     </row>
-    <row r="747">
+    <row r="747" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J747" s="3"/>
       <c r="K747" s="3"/>
     </row>
-    <row r="748">
+    <row r="748" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J748" s="3"/>
       <c r="K748" s="3"/>
     </row>
-    <row r="749">
+    <row r="749" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J749" s="3"/>
       <c r="K749" s="3"/>
     </row>
-    <row r="750">
+    <row r="750" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J750" s="3"/>
       <c r="K750" s="3"/>
     </row>
-    <row r="751">
+    <row r="751" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J751" s="3"/>
       <c r="K751" s="3"/>
     </row>
-    <row r="752">
+    <row r="752" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J752" s="3"/>
       <c r="K752" s="3"/>
     </row>
-    <row r="753">
+    <row r="753" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J753" s="3"/>
       <c r="K753" s="3"/>
     </row>
-    <row r="754">
+    <row r="754" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J754" s="3"/>
       <c r="K754" s="3"/>
     </row>
-    <row r="755">
+    <row r="755" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J755" s="3"/>
       <c r="K755" s="3"/>
     </row>
-    <row r="756">
+    <row r="756" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J756" s="3"/>
       <c r="K756" s="3"/>
     </row>
-    <row r="757">
+    <row r="757" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J757" s="3"/>
       <c r="K757" s="3"/>
     </row>
-    <row r="758">
+    <row r="758" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J758" s="3"/>
       <c r="K758" s="3"/>
     </row>
-    <row r="759">
+    <row r="759" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J759" s="3"/>
       <c r="K759" s="3"/>
     </row>
-    <row r="760">
+    <row r="760" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J760" s="3"/>
       <c r="K760" s="3"/>
     </row>
-    <row r="761">
+    <row r="761" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J761" s="3"/>
       <c r="K761" s="3"/>
     </row>
-    <row r="762">
+    <row r="762" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J762" s="3"/>
       <c r="K762" s="3"/>
     </row>
-    <row r="763">
+    <row r="763" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J763" s="3"/>
       <c r="K763" s="3"/>
     </row>
-    <row r="764">
+    <row r="764" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J764" s="3"/>
       <c r="K764" s="3"/>
     </row>
-    <row r="765">
+    <row r="765" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J765" s="3"/>
       <c r="K765" s="3"/>
     </row>
-    <row r="766">
+    <row r="766" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J766" s="3"/>
       <c r="K766" s="3"/>
     </row>
-    <row r="767">
+    <row r="767" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J767" s="3"/>
       <c r="K767" s="3"/>
     </row>
-    <row r="768">
+    <row r="768" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J768" s="3"/>
       <c r="K768" s="3"/>
     </row>
-    <row r="769">
+    <row r="769" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J769" s="3"/>
       <c r="K769" s="3"/>
     </row>
-    <row r="770">
+    <row r="770" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J770" s="3"/>
       <c r="K770" s="3"/>
     </row>
-    <row r="771">
+    <row r="771" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J771" s="3"/>
       <c r="K771" s="3"/>
     </row>
-    <row r="772">
+    <row r="772" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J772" s="3"/>
       <c r="K772" s="3"/>
     </row>
-    <row r="773">
+    <row r="773" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J773" s="3"/>
       <c r="K773" s="3"/>
     </row>
-    <row r="774">
+    <row r="774" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J774" s="3"/>
       <c r="K774" s="3"/>
     </row>
-    <row r="775">
+    <row r="775" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J775" s="3"/>
       <c r="K775" s="3"/>
     </row>
-    <row r="776">
+    <row r="776" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J776" s="3"/>
       <c r="K776" s="3"/>
     </row>
-    <row r="777">
+    <row r="777" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J777" s="3"/>
       <c r="K777" s="3"/>
     </row>
-    <row r="778">
+    <row r="778" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J778" s="3"/>
       <c r="K778" s="3"/>
     </row>
-    <row r="779">
+    <row r="779" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J779" s="3"/>
       <c r="K779" s="3"/>
     </row>
-    <row r="780">
+    <row r="780" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J780" s="3"/>
       <c r="K780" s="3"/>
     </row>
-    <row r="781">
+    <row r="781" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J781" s="3"/>
       <c r="K781" s="3"/>
     </row>
-    <row r="782">
+    <row r="782" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J782" s="3"/>
       <c r="K782" s="3"/>
     </row>
-    <row r="783">
+    <row r="783" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J783" s="3"/>
       <c r="K783" s="3"/>
     </row>
-    <row r="784">
+    <row r="784" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J784" s="3"/>
       <c r="K784" s="3"/>
     </row>
-    <row r="785">
+    <row r="785" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J785" s="3"/>
       <c r="K785" s="3"/>
     </row>
-    <row r="786">
+    <row r="786" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J786" s="3"/>
       <c r="K786" s="3"/>
     </row>
-    <row r="787">
+    <row r="787" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J787" s="3"/>
       <c r="K787" s="3"/>
     </row>
-    <row r="788">
+    <row r="788" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J788" s="3"/>
       <c r="K788" s="3"/>
     </row>
-    <row r="789">
+    <row r="789" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J789" s="3"/>
       <c r="K789" s="3"/>
     </row>
-    <row r="790">
+    <row r="790" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J790" s="3"/>
       <c r="K790" s="3"/>
     </row>
-    <row r="791">
+    <row r="791" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J791" s="3"/>
       <c r="K791" s="3"/>
     </row>
-    <row r="792">
+    <row r="792" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J792" s="3"/>
       <c r="K792" s="3"/>
     </row>
-    <row r="793">
+    <row r="793" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J793" s="3"/>
       <c r="K793" s="3"/>
     </row>
-    <row r="794">
+    <row r="794" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J794" s="3"/>
       <c r="K794" s="3"/>
     </row>
-    <row r="795">
+    <row r="795" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J795" s="3"/>
       <c r="K795" s="3"/>
     </row>
-    <row r="796">
+    <row r="796" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J796" s="3"/>
       <c r="K796" s="3"/>
     </row>
-    <row r="797">
+    <row r="797" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J797" s="3"/>
       <c r="K797" s="3"/>
     </row>
-    <row r="798">
+    <row r="798" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J798" s="3"/>
       <c r="K798" s="3"/>
     </row>
-    <row r="799">
+    <row r="799" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J799" s="3"/>
       <c r="K799" s="3"/>
     </row>
-    <row r="800">
+    <row r="800" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J800" s="3"/>
       <c r="K800" s="3"/>
     </row>
-    <row r="801">
+    <row r="801" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J801" s="3"/>
       <c r="K801" s="3"/>
     </row>
-    <row r="802">
+    <row r="802" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J802" s="3"/>
       <c r="K802" s="3"/>
     </row>
-    <row r="803">
+    <row r="803" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J803" s="3"/>
       <c r="K803" s="3"/>
     </row>
-    <row r="804">
+    <row r="804" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J804" s="3"/>
       <c r="K804" s="3"/>
     </row>
-    <row r="805">
+    <row r="805" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J805" s="3"/>
       <c r="K805" s="3"/>
     </row>
-    <row r="806">
+    <row r="806" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J806" s="3"/>
       <c r="K806" s="3"/>
     </row>
-    <row r="807">
+    <row r="807" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J807" s="3"/>
       <c r="K807" s="3"/>
     </row>
-    <row r="808">
+    <row r="808" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J808" s="3"/>
       <c r="K808" s="3"/>
     </row>
-    <row r="809">
+    <row r="809" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J809" s="3"/>
       <c r="K809" s="3"/>
     </row>
-    <row r="810">
+    <row r="810" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J810" s="3"/>
       <c r="K810" s="3"/>
     </row>
-    <row r="811">
+    <row r="811" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J811" s="3"/>
       <c r="K811" s="3"/>
     </row>
-    <row r="812">
+    <row r="812" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J812" s="3"/>
       <c r="K812" s="3"/>
     </row>
-    <row r="813">
+    <row r="813" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J813" s="3"/>
       <c r="K813" s="3"/>
     </row>
-    <row r="814">
+    <row r="814" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J814" s="3"/>
       <c r="K814" s="3"/>
     </row>
-    <row r="815">
+    <row r="815" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J815" s="3"/>
       <c r="K815" s="3"/>
     </row>
-    <row r="816">
+    <row r="816" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J816" s="3"/>
       <c r="K816" s="3"/>
     </row>
-    <row r="817">
+    <row r="817" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J817" s="3"/>
       <c r="K817" s="3"/>
     </row>
-    <row r="818">
+    <row r="818" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J818" s="3"/>
       <c r="K818" s="3"/>
     </row>
-    <row r="819">
+    <row r="819" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J819" s="3"/>
       <c r="K819" s="3"/>
     </row>
-    <row r="820">
+    <row r="820" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J820" s="3"/>
       <c r="K820" s="3"/>
     </row>
-    <row r="821">
+    <row r="821" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J821" s="3"/>
       <c r="K821" s="3"/>
     </row>
-    <row r="822">
+    <row r="822" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J822" s="3"/>
       <c r="K822" s="3"/>
     </row>
-    <row r="823">
+    <row r="823" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J823" s="3"/>
       <c r="K823" s="3"/>
     </row>
-    <row r="824">
+    <row r="824" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J824" s="3"/>
       <c r="K824" s="3"/>
     </row>
-    <row r="825">
+    <row r="825" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J825" s="3"/>
       <c r="K825" s="3"/>
     </row>
-    <row r="826">
+    <row r="826" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J826" s="3"/>
       <c r="K826" s="3"/>
     </row>
-    <row r="827">
+    <row r="827" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J827" s="3"/>
       <c r="K827" s="3"/>
     </row>
-    <row r="828">
+    <row r="828" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J828" s="3"/>
       <c r="K828" s="3"/>
     </row>
-    <row r="829">
+    <row r="829" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J829" s="3"/>
       <c r="K829" s="3"/>
     </row>
-    <row r="830">
+    <row r="830" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J830" s="3"/>
       <c r="K830" s="3"/>
     </row>
-    <row r="831">
+    <row r="831" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J831" s="3"/>
       <c r="K831" s="3"/>
     </row>
-    <row r="832">
+    <row r="832" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J832" s="3"/>
       <c r="K832" s="3"/>
     </row>
-    <row r="833">
+    <row r="833" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J833" s="3"/>
       <c r="K833" s="3"/>
     </row>
-    <row r="834">
+    <row r="834" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J834" s="3"/>
       <c r="K834" s="3"/>
     </row>
-    <row r="835">
+    <row r="835" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J835" s="3"/>
       <c r="K835" s="3"/>
     </row>
-    <row r="836">
+    <row r="836" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J836" s="3"/>
       <c r="K836" s="3"/>
     </row>
-    <row r="837">
+    <row r="837" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J837" s="3"/>
       <c r="K837" s="3"/>
     </row>
-    <row r="838">
+    <row r="838" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J838" s="3"/>
       <c r="K838" s="3"/>
     </row>
-    <row r="839">
+    <row r="839" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J839" s="3"/>
       <c r="K839" s="3"/>
     </row>
-    <row r="840">
+    <row r="840" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J840" s="3"/>
       <c r="K840" s="3"/>
     </row>
-    <row r="841">
+    <row r="841" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J841" s="3"/>
       <c r="K841" s="3"/>
     </row>
-    <row r="842">
+    <row r="842" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J842" s="3"/>
       <c r="K842" s="3"/>
     </row>
-    <row r="843">
+    <row r="843" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J843" s="3"/>
       <c r="K843" s="3"/>
     </row>
-    <row r="844">
+    <row r="844" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J844" s="3"/>
       <c r="K844" s="3"/>
     </row>
-    <row r="845">
+    <row r="845" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J845" s="3"/>
       <c r="K845" s="3"/>
     </row>
-    <row r="846">
+    <row r="846" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J846" s="3"/>
       <c r="K846" s="3"/>
     </row>
-    <row r="847">
+    <row r="847" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J847" s="3"/>
       <c r="K847" s="3"/>
     </row>
-    <row r="848">
+    <row r="848" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J848" s="3"/>
       <c r="K848" s="3"/>
     </row>
-    <row r="849">
+    <row r="849" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J849" s="3"/>
       <c r="K849" s="3"/>
     </row>
-    <row r="850">
+    <row r="850" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J850" s="3"/>
       <c r="K850" s="3"/>
     </row>
-    <row r="851">
+    <row r="851" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J851" s="3"/>
       <c r="K851" s="3"/>
     </row>
-    <row r="852">
+    <row r="852" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J852" s="3"/>
       <c r="K852" s="3"/>
     </row>
-    <row r="853">
+    <row r="853" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J853" s="3"/>
       <c r="K853" s="3"/>
     </row>
-    <row r="854">
+    <row r="854" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J854" s="3"/>
       <c r="K854" s="3"/>
     </row>
-    <row r="855">
+    <row r="855" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J855" s="3"/>
       <c r="K855" s="3"/>
     </row>
-    <row r="856">
+    <row r="856" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J856" s="3"/>
       <c r="K856" s="3"/>
     </row>
-    <row r="857">
+    <row r="857" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J857" s="3"/>
       <c r="K857" s="3"/>
     </row>
-    <row r="858">
+    <row r="858" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J858" s="3"/>
       <c r="K858" s="3"/>
     </row>
-    <row r="859">
+    <row r="859" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J859" s="3"/>
       <c r="K859" s="3"/>
     </row>
-    <row r="860">
+    <row r="860" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J860" s="3"/>
       <c r="K860" s="3"/>
     </row>
-    <row r="861">
+    <row r="861" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J861" s="3"/>
       <c r="K861" s="3"/>
     </row>
-    <row r="862">
+    <row r="862" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J862" s="3"/>
       <c r="K862" s="3"/>
     </row>
-    <row r="863">
+    <row r="863" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J863" s="3"/>
       <c r="K863" s="3"/>
     </row>
-    <row r="864">
+    <row r="864" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J864" s="3"/>
       <c r="K864" s="3"/>
     </row>
-    <row r="865">
+    <row r="865" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J865" s="3"/>
       <c r="K865" s="3"/>
     </row>
-    <row r="866">
+    <row r="866" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J866" s="3"/>
       <c r="K866" s="3"/>
     </row>
-    <row r="867">
+    <row r="867" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J867" s="3"/>
       <c r="K867" s="3"/>
     </row>
-    <row r="868">
+    <row r="868" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J868" s="3"/>
       <c r="K868" s="3"/>
     </row>
-    <row r="869">
+    <row r="869" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J869" s="3"/>
       <c r="K869" s="3"/>
     </row>
-    <row r="870">
+    <row r="870" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J870" s="3"/>
       <c r="K870" s="3"/>
     </row>
-    <row r="871">
+    <row r="871" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J871" s="3"/>
       <c r="K871" s="3"/>
     </row>
-    <row r="872">
+    <row r="872" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J872" s="3"/>
       <c r="K872" s="3"/>
     </row>
-    <row r="873">
+    <row r="873" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J873" s="3"/>
       <c r="K873" s="3"/>
     </row>
-    <row r="874">
+    <row r="874" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J874" s="3"/>
       <c r="K874" s="3"/>
     </row>
-    <row r="875">
+    <row r="875" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J875" s="3"/>
       <c r="K875" s="3"/>
     </row>
-    <row r="876">
+    <row r="876" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J876" s="3"/>
       <c r="K876" s="3"/>
     </row>
-    <row r="877">
+    <row r="877" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J877" s="3"/>
       <c r="K877" s="3"/>
     </row>
-    <row r="878">
+    <row r="878" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J878" s="3"/>
       <c r="K878" s="3"/>
     </row>
-    <row r="879">
+    <row r="879" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J879" s="3"/>
       <c r="K879" s="3"/>
     </row>
-    <row r="880">
+    <row r="880" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J880" s="3"/>
       <c r="K880" s="3"/>
     </row>
-    <row r="881">
+    <row r="881" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J881" s="3"/>
       <c r="K881" s="3"/>
     </row>
-    <row r="882">
+    <row r="882" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J882" s="3"/>
       <c r="K882" s="3"/>
     </row>
-    <row r="883">
+    <row r="883" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J883" s="3"/>
       <c r="K883" s="3"/>
     </row>
-    <row r="884">
+    <row r="884" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J884" s="3"/>
       <c r="K884" s="3"/>
     </row>
-    <row r="885">
+    <row r="885" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J885" s="3"/>
       <c r="K885" s="3"/>
     </row>
-    <row r="886">
+    <row r="886" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J886" s="3"/>
       <c r="K886" s="3"/>
     </row>
-    <row r="887">
+    <row r="887" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J887" s="3"/>
       <c r="K887" s="3"/>
     </row>
-    <row r="888">
+    <row r="888" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J888" s="3"/>
       <c r="K888" s="3"/>
     </row>
-    <row r="889">
+    <row r="889" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J889" s="3"/>
       <c r="K889" s="3"/>
     </row>
-    <row r="890">
+    <row r="890" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J890" s="3"/>
       <c r="K890" s="3"/>
     </row>
-    <row r="891">
+    <row r="891" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J891" s="3"/>
       <c r="K891" s="3"/>
     </row>
-    <row r="892">
+    <row r="892" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J892" s="3"/>
       <c r="K892" s="3"/>
     </row>
-    <row r="893">
+    <row r="893" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J893" s="3"/>
       <c r="K893" s="3"/>
     </row>
-    <row r="894">
+    <row r="894" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J894" s="3"/>
       <c r="K894" s="3"/>
     </row>
-    <row r="895">
+    <row r="895" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J895" s="3"/>
       <c r="K895" s="3"/>
     </row>
-    <row r="896">
+    <row r="896" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J896" s="3"/>
       <c r="K896" s="3"/>
     </row>
-    <row r="897">
+    <row r="897" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J897" s="3"/>
       <c r="K897" s="3"/>
     </row>
-    <row r="898">
+    <row r="898" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J898" s="3"/>
       <c r="K898" s="3"/>
     </row>
-    <row r="899">
+    <row r="899" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J899" s="3"/>
       <c r="K899" s="3"/>
     </row>
-    <row r="900">
+    <row r="900" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J900" s="3"/>
       <c r="K900" s="3"/>
     </row>
-    <row r="901">
+    <row r="901" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J901" s="3"/>
       <c r="K901" s="3"/>
     </row>
-    <row r="902">
+    <row r="902" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J902" s="3"/>
       <c r="K902" s="3"/>
     </row>
-    <row r="903">
+    <row r="903" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J903" s="3"/>
       <c r="K903" s="3"/>
     </row>
-    <row r="904">
+    <row r="904" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J904" s="3"/>
       <c r="K904" s="3"/>
     </row>
-    <row r="905">
+    <row r="905" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J905" s="3"/>
       <c r="K905" s="3"/>
     </row>
-    <row r="906">
+    <row r="906" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J906" s="3"/>
       <c r="K906" s="3"/>
     </row>
-    <row r="907">
+    <row r="907" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J907" s="3"/>
       <c r="K907" s="3"/>
     </row>
-    <row r="908">
+    <row r="908" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J908" s="3"/>
       <c r="K908" s="3"/>
     </row>
-    <row r="909">
+    <row r="909" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J909" s="3"/>
       <c r="K909" s="3"/>
     </row>
-    <row r="910">
+    <row r="910" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J910" s="3"/>
       <c r="K910" s="3"/>
     </row>
-    <row r="911">
+    <row r="911" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J911" s="3"/>
       <c r="K911" s="3"/>
     </row>
-    <row r="912">
+    <row r="912" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J912" s="3"/>
       <c r="K912" s="3"/>
     </row>
-    <row r="913">
+    <row r="913" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J913" s="3"/>
       <c r="K913" s="3"/>
     </row>
-    <row r="914">
+    <row r="914" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J914" s="3"/>
       <c r="K914" s="3"/>
     </row>
-    <row r="915">
+    <row r="915" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J915" s="3"/>
       <c r="K915" s="3"/>
     </row>
-    <row r="916">
+    <row r="916" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J916" s="3"/>
       <c r="K916" s="3"/>
     </row>
-    <row r="917">
+    <row r="917" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J917" s="3"/>
       <c r="K917" s="3"/>
     </row>
-    <row r="918">
+    <row r="918" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J918" s="3"/>
       <c r="K918" s="3"/>
     </row>
-    <row r="919">
+    <row r="919" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J919" s="3"/>
       <c r="K919" s="3"/>
     </row>
-    <row r="920">
+    <row r="920" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J920" s="3"/>
       <c r="K920" s="3"/>
     </row>
-    <row r="921">
+    <row r="921" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J921" s="3"/>
       <c r="K921" s="3"/>
     </row>
-    <row r="922">
+    <row r="922" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J922" s="3"/>
       <c r="K922" s="3"/>
     </row>
-    <row r="923">
+    <row r="923" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J923" s="3"/>
       <c r="K923" s="3"/>
     </row>
-    <row r="924">
+    <row r="924" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J924" s="3"/>
       <c r="K924" s="3"/>
     </row>
-    <row r="925">
+    <row r="925" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J925" s="3"/>
       <c r="K925" s="3"/>
     </row>
-    <row r="926">
+    <row r="926" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J926" s="3"/>
       <c r="K926" s="3"/>
     </row>
-    <row r="927">
+    <row r="927" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J927" s="3"/>
       <c r="K927" s="3"/>
     </row>
-    <row r="928">
+    <row r="928" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J928" s="3"/>
       <c r="K928" s="3"/>
     </row>
-    <row r="929">
+    <row r="929" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J929" s="3"/>
       <c r="K929" s="3"/>
     </row>
-    <row r="930">
+    <row r="930" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J930" s="3"/>
       <c r="K930" s="3"/>
     </row>
-    <row r="931">
+    <row r="931" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J931" s="3"/>
       <c r="K931" s="3"/>
     </row>
-    <row r="932">
+    <row r="932" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J932" s="3"/>
       <c r="K932" s="3"/>
     </row>
-    <row r="933">
+    <row r="933" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J933" s="3"/>
       <c r="K933" s="3"/>
     </row>
-    <row r="934">
+    <row r="934" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J934" s="3"/>
       <c r="K934" s="3"/>
     </row>
-    <row r="935">
+    <row r="935" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J935" s="3"/>
       <c r="K935" s="3"/>
     </row>
-    <row r="936">
+    <row r="936" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J936" s="3"/>
       <c r="K936" s="3"/>
     </row>
-    <row r="937">
+    <row r="937" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J937" s="3"/>
       <c r="K937" s="3"/>
     </row>
-    <row r="938">
+    <row r="938" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J938" s="3"/>
       <c r="K938" s="3"/>
     </row>
-    <row r="939">
+    <row r="939" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J939" s="3"/>
       <c r="K939" s="3"/>
     </row>
-    <row r="940">
+    <row r="940" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J940" s="3"/>
       <c r="K940" s="3"/>
     </row>
-    <row r="941">
+    <row r="941" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J941" s="3"/>
       <c r="K941" s="3"/>
     </row>
-    <row r="942">
+    <row r="942" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J942" s="3"/>
       <c r="K942" s="3"/>
     </row>
-    <row r="943">
+    <row r="943" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J943" s="3"/>
       <c r="K943" s="3"/>
     </row>
-    <row r="944">
+    <row r="944" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J944" s="3"/>
       <c r="K944" s="3"/>
     </row>
-    <row r="945">
+    <row r="945" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J945" s="3"/>
       <c r="K945" s="3"/>
     </row>
-    <row r="946">
+    <row r="946" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J946" s="3"/>
       <c r="K946" s="3"/>
     </row>
-    <row r="947">
+    <row r="947" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J947" s="3"/>
       <c r="K947" s="3"/>
     </row>
-    <row r="948">
+    <row r="948" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J948" s="3"/>
       <c r="K948" s="3"/>
     </row>
-    <row r="949">
+    <row r="949" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J949" s="3"/>
       <c r="K949" s="3"/>
     </row>
-    <row r="950">
+    <row r="950" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J950" s="3"/>
       <c r="K950" s="3"/>
     </row>
-    <row r="951">
+    <row r="951" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J951" s="3"/>
       <c r="K951" s="3"/>
     </row>
-    <row r="952">
+    <row r="952" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J952" s="3"/>
       <c r="K952" s="3"/>
     </row>
-    <row r="953">
+    <row r="953" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J953" s="3"/>
       <c r="K953" s="3"/>
     </row>
-    <row r="954">
+    <row r="954" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J954" s="3"/>
       <c r="K954" s="3"/>
     </row>
-    <row r="955">
+    <row r="955" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J955" s="3"/>
       <c r="K955" s="3"/>
     </row>
-    <row r="956">
+    <row r="956" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J956" s="3"/>
       <c r="K956" s="3"/>
     </row>
-    <row r="957">
+    <row r="957" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J957" s="3"/>
       <c r="K957" s="3"/>
     </row>
-    <row r="958">
+    <row r="958" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J958" s="3"/>
       <c r="K958" s="3"/>
     </row>
-    <row r="959">
+    <row r="959" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J959" s="3"/>
       <c r="K959" s="3"/>
     </row>
-    <row r="960">
+    <row r="960" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J960" s="3"/>
       <c r="K960" s="3"/>
     </row>
-    <row r="961">
+    <row r="961" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J961" s="3"/>
       <c r="K961" s="3"/>
     </row>
-    <row r="962">
+    <row r="962" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J962" s="3"/>
       <c r="K962" s="3"/>
     </row>
-    <row r="963">
+    <row r="963" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J963" s="3"/>
       <c r="K963" s="3"/>
     </row>
-    <row r="964">
+    <row r="964" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J964" s="3"/>
       <c r="K964" s="3"/>
     </row>
-    <row r="965">
+    <row r="965" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J965" s="3"/>
       <c r="K965" s="3"/>
     </row>
-    <row r="966">
+    <row r="966" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J966" s="3"/>
       <c r="K966" s="3"/>
     </row>
-    <row r="967">
+    <row r="967" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J967" s="3"/>
       <c r="K967" s="3"/>
     </row>
-    <row r="968">
+    <row r="968" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J968" s="3"/>
       <c r="K968" s="3"/>
     </row>
-    <row r="969">
+    <row r="969" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J969" s="3"/>
       <c r="K969" s="3"/>
     </row>
-    <row r="970">
+    <row r="970" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J970" s="3"/>
       <c r="K970" s="3"/>
     </row>
-    <row r="971">
+    <row r="971" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J971" s="3"/>
       <c r="K971" s="3"/>
     </row>
-    <row r="972">
+    <row r="972" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J972" s="3"/>
       <c r="K972" s="3"/>
     </row>
-    <row r="973">
+    <row r="973" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J973" s="3"/>
       <c r="K973" s="3"/>
     </row>
-    <row r="974">
+    <row r="974" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J974" s="3"/>
       <c r="K974" s="3"/>
     </row>
-    <row r="975">
+    <row r="975" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J975" s="3"/>
       <c r="K975" s="3"/>
     </row>
-    <row r="976">
+    <row r="976" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J976" s="3"/>
       <c r="K976" s="3"/>
     </row>
-    <row r="977">
+    <row r="977" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J977" s="3"/>
       <c r="K977" s="3"/>
     </row>
-    <row r="978">
+    <row r="978" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J978" s="3"/>
       <c r="K978" s="3"/>
     </row>
-    <row r="979">
+    <row r="979" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J979" s="3"/>
       <c r="K979" s="3"/>
     </row>
-    <row r="980">
+    <row r="980" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J980" s="3"/>
       <c r="K980" s="3"/>
     </row>
-    <row r="981">
+    <row r="981" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J981" s="3"/>
       <c r="K981" s="3"/>
     </row>
-    <row r="982">
+    <row r="982" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J982" s="3"/>
       <c r="K982" s="3"/>
     </row>
-    <row r="983">
+    <row r="983" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J983" s="3"/>
       <c r="K983" s="3"/>
     </row>
-    <row r="984">
+    <row r="984" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J984" s="3"/>
       <c r="K984" s="3"/>
     </row>
-    <row r="985">
+    <row r="985" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J985" s="3"/>
       <c r="K985" s="3"/>
     </row>
-    <row r="986">
+    <row r="986" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J986" s="3"/>
       <c r="K986" s="3"/>
     </row>
-    <row r="987">
+    <row r="987" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J987" s="3"/>
       <c r="K987" s="3"/>
     </row>
-    <row r="988">
+    <row r="988" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J988" s="3"/>
       <c r="K988" s="3"/>
     </row>
-    <row r="989">
+    <row r="989" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J989" s="3"/>
       <c r="K989" s="3"/>
     </row>
-    <row r="990">
+    <row r="990" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J990" s="3"/>
       <c r="K990" s="3"/>
     </row>
-    <row r="991">
+    <row r="991" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J991" s="3"/>
       <c r="K991" s="3"/>
     </row>
-    <row r="992">
+    <row r="992" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J992" s="3"/>
       <c r="K992" s="3"/>
     </row>
-    <row r="993">
+    <row r="993" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J993" s="3"/>
       <c r="K993" s="3"/>
     </row>
-    <row r="994">
+    <row r="994" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J994" s="3"/>
       <c r="K994" s="3"/>
     </row>
-    <row r="995">
+    <row r="995" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J995" s="3"/>
       <c r="K995" s="3"/>
     </row>
-    <row r="996">
+    <row r="996" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J996" s="3"/>
       <c r="K996" s="3"/>
     </row>
-    <row r="997">
+    <row r="997" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J997" s="3"/>
       <c r="K997" s="3"/>
     </row>
-    <row r="998">
+    <row r="998" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J998" s="3"/>
       <c r="K998" s="3"/>
     </row>
-    <row r="999">
+    <row r="999" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J999" s="3"/>
       <c r="K999" s="3"/>
     </row>
-    <row r="1000">
+    <row r="1000" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J1000" s="3"/>
       <c r="K1000" s="3"/>
     </row>
-    <row r="1001">
+    <row r="1001" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J1001" s="3"/>
       <c r="K1001" s="3"/>
     </row>
-    <row r="1002">
+    <row r="1002" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J1002" s="3"/>
       <c r="K1002" s="3"/>
     </row>
-    <row r="1003">
+    <row r="1003" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J1003" s="3"/>
       <c r="K1003" s="3"/>
     </row>
-    <row r="1004">
+    <row r="1004" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J1004" s="3"/>
       <c r="K1004" s="3"/>
     </row>
-    <row r="1005">
+    <row r="1005" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J1005" s="3"/>
       <c r="K1005" s="3"/>
     </row>
-    <row r="1006">
+    <row r="1006" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J1006" s="3"/>
       <c r="K1006" s="3"/>
     </row>
-    <row r="1007">
+    <row r="1007" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J1007" s="3"/>
       <c r="K1007" s="3"/>
     </row>
-    <row r="1008">
+    <row r="1008" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J1008" s="3"/>
       <c r="K1008" s="3"/>
     </row>
-    <row r="1009">
+    <row r="1009" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J1009" s="3"/>
       <c r="K1009" s="3"/>
     </row>
-    <row r="1010">
+    <row r="1010" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J1010" s="3"/>
       <c r="K1010" s="3"/>
     </row>
@@ -4754,1060 +5114,1478 @@
     <mergeCell ref="A13:J13"/>
     <mergeCell ref="A14:J14"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F103"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="18.88"/>
-    <col customWidth="1" min="4" max="4" width="25.13"/>
-    <col customWidth="1" min="5" max="5" width="12.63"/>
-    <col customWidth="1" min="6" max="6" width="100.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="25.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="100.13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+    </row>
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="17" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="s">
+      <c r="B4" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B7" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="B9" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="B10" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="B11" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="B12" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="17" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7">
-        <v>5.0</v>
-      </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7">
-        <v>7.0</v>
-      </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7">
-        <v>8.0</v>
-      </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7">
-        <v>9.0</v>
-      </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7">
-        <v>10.0</v>
-      </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7">
-        <v>11.0</v>
-      </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7">
-        <v>12.0</v>
-      </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7">
-        <v>13.0</v>
-      </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7">
-        <v>14.0</v>
-      </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7">
-        <v>16.0</v>
-      </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7">
-        <v>17.0</v>
-      </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7">
-        <v>18.0</v>
-      </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7">
-        <v>19.0</v>
-      </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7">
-        <v>20.0</v>
-      </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7">
-        <v>21.0</v>
-      </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7">
-        <v>22.0</v>
-      </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7">
-        <v>23.0</v>
-      </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7">
-        <v>24.0</v>
-      </c>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7">
-        <v>25.0</v>
-      </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7">
-        <v>26.0</v>
-      </c>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7">
-        <v>27.0</v>
-      </c>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7">
-        <v>28.0</v>
-      </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7">
-        <v>29.0</v>
-      </c>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7">
-        <v>30.0</v>
-      </c>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7">
-        <v>31.0</v>
-      </c>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7">
-        <v>32.0</v>
-      </c>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7">
-        <v>33.0</v>
-      </c>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7">
-        <v>34.0</v>
-      </c>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7">
-        <v>35.0</v>
-      </c>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7">
-        <v>36.0</v>
-      </c>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7">
-        <v>37.0</v>
-      </c>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7">
-        <v>38.0</v>
-      </c>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7">
-        <v>39.0</v>
-      </c>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7">
-        <v>40.0</v>
-      </c>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="7">
-        <v>41.0</v>
-      </c>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7">
-        <v>42.0</v>
-      </c>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="7">
-        <v>43.0</v>
-      </c>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="7">
-        <v>44.0</v>
-      </c>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="7">
-        <v>45.0</v>
-      </c>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="7">
-        <v>46.0</v>
-      </c>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="7">
-        <v>47.0</v>
-      </c>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="7">
-        <v>48.0</v>
-      </c>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="7">
-        <v>49.0</v>
-      </c>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="7">
-        <v>50.0</v>
-      </c>
-      <c r="B53" s="8"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="7">
-        <v>51.0</v>
-      </c>
-      <c r="B54" s="8"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="7">
-        <v>52.0</v>
-      </c>
-      <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="7">
-        <v>53.0</v>
-      </c>
-      <c r="B56" s="8"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="7">
-        <v>54.0</v>
-      </c>
-      <c r="B57" s="8"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="7">
-        <v>55.0</v>
-      </c>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="7">
-        <v>56.0</v>
-      </c>
-      <c r="B59" s="8"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="7">
-        <v>57.0</v>
-      </c>
-      <c r="B60" s="8"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="7">
-        <v>58.0</v>
-      </c>
-      <c r="B61" s="8"/>
-      <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="7">
-        <v>59.0</v>
-      </c>
-      <c r="B62" s="8"/>
-      <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="8"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="7">
-        <v>60.0</v>
-      </c>
-      <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="8"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="7">
-        <v>61.0</v>
-      </c>
-      <c r="B64" s="8"/>
-      <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="8"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="7">
-        <v>62.0</v>
-      </c>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="7">
-        <v>63.0</v>
-      </c>
-      <c r="B66" s="8"/>
-      <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="7">
-        <v>64.0</v>
-      </c>
-      <c r="B67" s="8"/>
-      <c r="C67" s="8"/>
-      <c r="D67" s="8"/>
-      <c r="E67" s="8"/>
-      <c r="F67" s="8"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="7">
-        <v>65.0</v>
-      </c>
-      <c r="B68" s="8"/>
-      <c r="C68" s="8"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="7">
-        <v>66.0</v>
-      </c>
-      <c r="B69" s="8"/>
-      <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="7">
-        <v>67.0</v>
-      </c>
-      <c r="B70" s="8"/>
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="7">
-        <v>68.0</v>
-      </c>
-      <c r="B71" s="8"/>
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="7">
-        <v>69.0</v>
-      </c>
-      <c r="B72" s="8"/>
-      <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="8"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="7">
-        <v>70.0</v>
-      </c>
-      <c r="B73" s="8"/>
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="7">
-        <v>71.0</v>
-      </c>
-      <c r="B74" s="8"/>
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="8"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="7">
-        <v>72.0</v>
-      </c>
-      <c r="B75" s="8"/>
-      <c r="C75" s="8"/>
-      <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="8"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="7">
-        <v>73.0</v>
-      </c>
-      <c r="B76" s="8"/>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="8"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="7">
-        <v>74.0</v>
-      </c>
-      <c r="B77" s="8"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="7">
-        <v>75.0</v>
-      </c>
-      <c r="B78" s="8"/>
-      <c r="C78" s="8"/>
-      <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="8"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="7">
-        <v>76.0</v>
-      </c>
-      <c r="B79" s="8"/>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="8"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="7">
-        <v>77.0</v>
-      </c>
-      <c r="B80" s="8"/>
-      <c r="C80" s="8"/>
-      <c r="D80" s="8"/>
-      <c r="E80" s="8"/>
-      <c r="F80" s="8"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="7">
-        <v>78.0</v>
-      </c>
-      <c r="B81" s="8"/>
-      <c r="C81" s="8"/>
-      <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
-      <c r="F81" s="8"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="7">
-        <v>79.0</v>
-      </c>
-      <c r="B82" s="8"/>
-      <c r="C82" s="8"/>
-      <c r="D82" s="8"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="8"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="7">
-        <v>80.0</v>
-      </c>
-      <c r="B83" s="8"/>
-      <c r="C83" s="8"/>
-      <c r="D83" s="8"/>
-      <c r="E83" s="8"/>
-      <c r="F83" s="8"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="7">
-        <v>81.0</v>
-      </c>
-      <c r="B84" s="8"/>
-      <c r="C84" s="8"/>
-      <c r="D84" s="8"/>
-      <c r="E84" s="8"/>
-      <c r="F84" s="8"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="7">
-        <v>82.0</v>
-      </c>
-      <c r="B85" s="8"/>
-      <c r="C85" s="8"/>
-      <c r="D85" s="8"/>
-      <c r="E85" s="8"/>
-      <c r="F85" s="8"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="7">
-        <v>83.0</v>
-      </c>
-      <c r="B86" s="8"/>
-      <c r="C86" s="8"/>
-      <c r="D86" s="8"/>
-      <c r="E86" s="8"/>
-      <c r="F86" s="8"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="7">
-        <v>84.0</v>
-      </c>
-      <c r="B87" s="8"/>
-      <c r="C87" s="8"/>
-      <c r="D87" s="8"/>
-      <c r="E87" s="8"/>
-      <c r="F87" s="8"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="7">
-        <v>85.0</v>
-      </c>
-      <c r="B88" s="8"/>
-      <c r="C88" s="8"/>
-      <c r="D88" s="8"/>
-      <c r="E88" s="8"/>
-      <c r="F88" s="8"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="7">
-        <v>86.0</v>
-      </c>
-      <c r="B89" s="8"/>
-      <c r="C89" s="8"/>
-      <c r="D89" s="8"/>
-      <c r="E89" s="8"/>
-      <c r="F89" s="8"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="7">
-        <v>87.0</v>
-      </c>
-      <c r="B90" s="8"/>
-      <c r="C90" s="8"/>
-      <c r="D90" s="8"/>
-      <c r="E90" s="8"/>
-      <c r="F90" s="8"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="7">
-        <v>88.0</v>
-      </c>
-      <c r="B91" s="8"/>
-      <c r="C91" s="8"/>
-      <c r="D91" s="8"/>
-      <c r="E91" s="8"/>
-      <c r="F91" s="8"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="7">
-        <v>89.0</v>
-      </c>
-      <c r="B92" s="8"/>
-      <c r="C92" s="8"/>
-      <c r="D92" s="8"/>
-      <c r="E92" s="8"/>
-      <c r="F92" s="8"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="7">
-        <v>90.0</v>
-      </c>
-      <c r="B93" s="8"/>
-      <c r="C93" s="8"/>
-      <c r="D93" s="8"/>
-      <c r="E93" s="8"/>
-      <c r="F93" s="8"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="7">
-        <v>91.0</v>
-      </c>
-      <c r="B94" s="8"/>
-      <c r="C94" s="8"/>
-      <c r="D94" s="8"/>
-      <c r="E94" s="8"/>
-      <c r="F94" s="8"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="7">
-        <v>92.0</v>
-      </c>
-      <c r="B95" s="8"/>
-      <c r="C95" s="8"/>
-      <c r="D95" s="8"/>
-      <c r="E95" s="8"/>
-      <c r="F95" s="8"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="7">
-        <v>93.0</v>
-      </c>
-      <c r="B96" s="8"/>
-      <c r="C96" s="8"/>
-      <c r="D96" s="8"/>
-      <c r="E96" s="8"/>
-      <c r="F96" s="8"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="7">
-        <v>94.0</v>
-      </c>
-      <c r="B97" s="8"/>
-      <c r="C97" s="8"/>
-      <c r="D97" s="8"/>
-      <c r="E97" s="8"/>
-      <c r="F97" s="8"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="7">
-        <v>95.0</v>
-      </c>
-      <c r="B98" s="8"/>
-      <c r="C98" s="8"/>
-      <c r="D98" s="8"/>
-      <c r="E98" s="8"/>
-      <c r="F98" s="8"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="7">
-        <v>96.0</v>
-      </c>
-      <c r="B99" s="8"/>
-      <c r="C99" s="8"/>
-      <c r="D99" s="8"/>
-      <c r="E99" s="8"/>
-      <c r="F99" s="8"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="7">
-        <v>97.0</v>
-      </c>
-      <c r="B100" s="8"/>
-      <c r="C100" s="8"/>
-      <c r="D100" s="8"/>
-      <c r="E100" s="8"/>
-      <c r="F100" s="8"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="7">
-        <v>98.0</v>
-      </c>
-      <c r="B101" s="8"/>
-      <c r="C101" s="8"/>
-      <c r="D101" s="8"/>
-      <c r="E101" s="8"/>
-      <c r="F101" s="8"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="7">
-        <v>99.0</v>
-      </c>
-      <c r="B102" s="8"/>
-      <c r="C102" s="8"/>
-      <c r="D102" s="8"/>
-      <c r="E102" s="8"/>
-      <c r="F102" s="8"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="7">
-        <v>100.0</v>
-      </c>
-      <c r="B103" s="8"/>
-      <c r="C103" s="8"/>
-      <c r="D103" s="8"/>
-      <c r="E103" s="8"/>
-      <c r="F103" s="8"/>
+      <c r="B13" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F27" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F36" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F37" s="17" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F39" s="17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D43" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="17"/>
+    </row>
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="17"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="17"/>
+    </row>
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="17"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="17"/>
+    </row>
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="17"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="17"/>
+    </row>
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
+    </row>
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="17"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="17"/>
+    </row>
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="17"/>
+    </row>
+    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="17"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
+      <c r="F51" s="17"/>
+    </row>
+    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="17" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="17"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="17"/>
+    </row>
+    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" s="17"/>
+      <c r="C53" s="17"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
+      <c r="F53" s="17"/>
+    </row>
+    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="17" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" s="17"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="17"/>
+    </row>
+    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" s="17"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
+      <c r="F55" s="17"/>
+    </row>
+    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="17" t="n">
+        <v>53</v>
+      </c>
+      <c r="B56" s="17"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
+      <c r="F56" s="17"/>
+    </row>
+    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="17" t="n">
+        <v>54</v>
+      </c>
+      <c r="B57" s="17"/>
+      <c r="C57" s="17"/>
+      <c r="D57" s="17"/>
+      <c r="E57" s="17"/>
+      <c r="F57" s="17"/>
+    </row>
+    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" s="17"/>
+      <c r="C58" s="17"/>
+      <c r="D58" s="17"/>
+      <c r="E58" s="17"/>
+      <c r="F58" s="17"/>
+    </row>
+    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="17" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="17"/>
+      <c r="C59" s="17"/>
+      <c r="D59" s="17"/>
+      <c r="E59" s="17"/>
+      <c r="F59" s="17"/>
+    </row>
+    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" s="17"/>
+      <c r="C60" s="17"/>
+      <c r="D60" s="17"/>
+      <c r="E60" s="17"/>
+      <c r="F60" s="17"/>
+    </row>
+    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="17" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" s="17"/>
+      <c r="C61" s="17"/>
+      <c r="D61" s="17"/>
+      <c r="E61" s="17"/>
+      <c r="F61" s="17"/>
+    </row>
+    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="17" t="n">
+        <v>59</v>
+      </c>
+      <c r="B62" s="17"/>
+      <c r="C62" s="17"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="17"/>
+      <c r="F62" s="17"/>
+    </row>
+    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="B63" s="17"/>
+      <c r="C63" s="17"/>
+      <c r="D63" s="17"/>
+      <c r="E63" s="17"/>
+      <c r="F63" s="17"/>
+    </row>
+    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="B64" s="17"/>
+      <c r="C64" s="17"/>
+      <c r="D64" s="17"/>
+      <c r="E64" s="17"/>
+      <c r="F64" s="17"/>
+    </row>
+    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="B65" s="17"/>
+      <c r="C65" s="17"/>
+      <c r="D65" s="17"/>
+      <c r="E65" s="17"/>
+      <c r="F65" s="17"/>
+    </row>
+    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="17" t="n">
+        <v>63</v>
+      </c>
+      <c r="B66" s="17"/>
+      <c r="C66" s="17"/>
+      <c r="D66" s="17"/>
+      <c r="E66" s="17"/>
+      <c r="F66" s="17"/>
+    </row>
+    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="17" t="n">
+        <v>64</v>
+      </c>
+      <c r="B67" s="17"/>
+      <c r="C67" s="17"/>
+      <c r="D67" s="17"/>
+      <c r="E67" s="17"/>
+      <c r="F67" s="17"/>
+    </row>
+    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="B68" s="17"/>
+      <c r="C68" s="17"/>
+      <c r="D68" s="17"/>
+      <c r="E68" s="17"/>
+      <c r="F68" s="17"/>
+    </row>
+    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="17" t="n">
+        <v>66</v>
+      </c>
+      <c r="B69" s="17"/>
+      <c r="C69" s="17"/>
+      <c r="D69" s="17"/>
+      <c r="E69" s="17"/>
+      <c r="F69" s="17"/>
+    </row>
+    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="17" t="n">
+        <v>67</v>
+      </c>
+      <c r="B70" s="17"/>
+      <c r="C70" s="17"/>
+      <c r="D70" s="17"/>
+      <c r="E70" s="17"/>
+      <c r="F70" s="17"/>
+    </row>
+    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="17" t="n">
+        <v>68</v>
+      </c>
+      <c r="B71" s="17"/>
+      <c r="C71" s="17"/>
+      <c r="D71" s="17"/>
+      <c r="E71" s="17"/>
+      <c r="F71" s="17"/>
+    </row>
+    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="17" t="n">
+        <v>69</v>
+      </c>
+      <c r="B72" s="17"/>
+      <c r="C72" s="17"/>
+      <c r="D72" s="17"/>
+      <c r="E72" s="17"/>
+      <c r="F72" s="17"/>
+    </row>
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="B73" s="17"/>
+      <c r="C73" s="17"/>
+      <c r="D73" s="17"/>
+      <c r="E73" s="17"/>
+      <c r="F73" s="17"/>
+    </row>
+    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="17" t="n">
+        <v>71</v>
+      </c>
+      <c r="B74" s="17"/>
+      <c r="C74" s="17"/>
+      <c r="D74" s="17"/>
+      <c r="E74" s="17"/>
+      <c r="F74" s="17"/>
+    </row>
+    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="17" t="n">
+        <v>72</v>
+      </c>
+      <c r="B75" s="17"/>
+      <c r="C75" s="17"/>
+      <c r="D75" s="17"/>
+      <c r="E75" s="17"/>
+      <c r="F75" s="17"/>
+    </row>
+    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="17" t="n">
+        <v>73</v>
+      </c>
+      <c r="B76" s="17"/>
+      <c r="C76" s="17"/>
+      <c r="D76" s="17"/>
+      <c r="E76" s="17"/>
+      <c r="F76" s="17"/>
+    </row>
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="17" t="n">
+        <v>74</v>
+      </c>
+      <c r="B77" s="17"/>
+      <c r="C77" s="17"/>
+      <c r="D77" s="17"/>
+      <c r="E77" s="17"/>
+      <c r="F77" s="17"/>
+    </row>
+    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="17" t="n">
+        <v>75</v>
+      </c>
+      <c r="B78" s="17"/>
+      <c r="C78" s="17"/>
+      <c r="D78" s="17"/>
+      <c r="E78" s="17"/>
+      <c r="F78" s="17"/>
+    </row>
+    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="17" t="n">
+        <v>76</v>
+      </c>
+      <c r="B79" s="17"/>
+      <c r="C79" s="17"/>
+      <c r="D79" s="17"/>
+      <c r="E79" s="17"/>
+      <c r="F79" s="17"/>
+    </row>
+    <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="17" t="n">
+        <v>77</v>
+      </c>
+      <c r="B80" s="17"/>
+      <c r="C80" s="17"/>
+      <c r="D80" s="17"/>
+      <c r="E80" s="17"/>
+      <c r="F80" s="17"/>
+    </row>
+    <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="B81" s="17"/>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+    </row>
+    <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="17" t="n">
+        <v>79</v>
+      </c>
+      <c r="B82" s="17"/>
+      <c r="C82" s="17"/>
+      <c r="D82" s="17"/>
+      <c r="E82" s="17"/>
+      <c r="F82" s="17"/>
+    </row>
+    <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="B83" s="17"/>
+      <c r="C83" s="17"/>
+      <c r="D83" s="17"/>
+      <c r="E83" s="17"/>
+      <c r="F83" s="17"/>
+    </row>
+    <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="17" t="n">
+        <v>81</v>
+      </c>
+      <c r="B84" s="17"/>
+      <c r="C84" s="17"/>
+      <c r="D84" s="17"/>
+      <c r="E84" s="17"/>
+      <c r="F84" s="17"/>
+    </row>
+    <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="17" t="n">
+        <v>82</v>
+      </c>
+      <c r="B85" s="17"/>
+      <c r="C85" s="17"/>
+      <c r="D85" s="17"/>
+      <c r="E85" s="17"/>
+      <c r="F85" s="17"/>
+    </row>
+    <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="17" t="n">
+        <v>83</v>
+      </c>
+      <c r="B86" s="17"/>
+      <c r="C86" s="17"/>
+      <c r="D86" s="17"/>
+      <c r="E86" s="17"/>
+      <c r="F86" s="17"/>
+    </row>
+    <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="B87" s="17"/>
+      <c r="C87" s="17"/>
+      <c r="D87" s="17"/>
+      <c r="E87" s="17"/>
+      <c r="F87" s="17"/>
+    </row>
+    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="17" t="n">
+        <v>85</v>
+      </c>
+      <c r="B88" s="17"/>
+      <c r="C88" s="17"/>
+      <c r="D88" s="17"/>
+      <c r="E88" s="17"/>
+      <c r="F88" s="17"/>
+    </row>
+    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="17" t="n">
+        <v>86</v>
+      </c>
+      <c r="B89" s="17"/>
+      <c r="C89" s="17"/>
+      <c r="D89" s="17"/>
+      <c r="E89" s="17"/>
+      <c r="F89" s="17"/>
+    </row>
+    <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="17" t="n">
+        <v>87</v>
+      </c>
+      <c r="B90" s="17"/>
+      <c r="C90" s="17"/>
+      <c r="D90" s="17"/>
+      <c r="E90" s="17"/>
+      <c r="F90" s="17"/>
+    </row>
+    <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="17" t="n">
+        <v>88</v>
+      </c>
+      <c r="B91" s="17"/>
+      <c r="C91" s="17"/>
+      <c r="D91" s="17"/>
+      <c r="E91" s="17"/>
+      <c r="F91" s="17"/>
+    </row>
+    <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="17" t="n">
+        <v>89</v>
+      </c>
+      <c r="B92" s="17"/>
+      <c r="C92" s="17"/>
+      <c r="D92" s="17"/>
+      <c r="E92" s="17"/>
+      <c r="F92" s="17"/>
+    </row>
+    <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="B93" s="17"/>
+      <c r="C93" s="17"/>
+      <c r="D93" s="17"/>
+      <c r="E93" s="17"/>
+      <c r="F93" s="17"/>
+    </row>
+    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="17" t="n">
+        <v>91</v>
+      </c>
+      <c r="B94" s="17"/>
+      <c r="C94" s="17"/>
+      <c r="D94" s="17"/>
+      <c r="E94" s="17"/>
+      <c r="F94" s="17"/>
+    </row>
+    <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="17" t="n">
+        <v>92</v>
+      </c>
+      <c r="B95" s="17"/>
+      <c r="C95" s="17"/>
+      <c r="D95" s="17"/>
+      <c r="E95" s="17"/>
+      <c r="F95" s="17"/>
+    </row>
+    <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="17" t="n">
+        <v>93</v>
+      </c>
+      <c r="B96" s="17"/>
+      <c r="C96" s="17"/>
+      <c r="D96" s="17"/>
+      <c r="E96" s="17"/>
+      <c r="F96" s="17"/>
+    </row>
+    <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="17" t="n">
+        <v>94</v>
+      </c>
+      <c r="B97" s="17"/>
+      <c r="C97" s="17"/>
+      <c r="D97" s="17"/>
+      <c r="E97" s="17"/>
+      <c r="F97" s="17"/>
+    </row>
+    <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="17" t="n">
+        <v>95</v>
+      </c>
+      <c r="B98" s="17"/>
+      <c r="C98" s="17"/>
+      <c r="D98" s="17"/>
+      <c r="E98" s="17"/>
+      <c r="F98" s="17"/>
+    </row>
+    <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="17" t="n">
+        <v>96</v>
+      </c>
+      <c r="B99" s="17"/>
+      <c r="C99" s="17"/>
+      <c r="D99" s="17"/>
+      <c r="E99" s="17"/>
+      <c r="F99" s="17"/>
+    </row>
+    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="17" t="n">
+        <v>97</v>
+      </c>
+      <c r="B100" s="17"/>
+      <c r="C100" s="17"/>
+      <c r="D100" s="17"/>
+      <c r="E100" s="17"/>
+      <c r="F100" s="17"/>
+    </row>
+    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="17" t="n">
+        <v>98</v>
+      </c>
+      <c r="B101" s="17"/>
+      <c r="C101" s="17"/>
+      <c r="D101" s="17"/>
+      <c r="E101" s="17"/>
+      <c r="F101" s="17"/>
+    </row>
+    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="17" t="n">
+        <v>99</v>
+      </c>
+      <c r="B102" s="17"/>
+      <c r="C102" s="17"/>
+      <c r="D102" s="17"/>
+      <c r="E102" s="17"/>
+      <c r="F102" s="17"/>
+    </row>
+    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="B103" s="17"/>
+      <c r="C103" s="17"/>
+      <c r="D103" s="17"/>
+      <c r="E103" s="17"/>
+      <c r="F103" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>